--- a/datacontract/templates/excel/odcs-template.xlsx
+++ b/datacontract/templates/excel/odcs-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fb/IdeaProjects/entropy-data/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="508" documentId="13_ncr:1_{C1AEC928-3B3E-6A48-BC07-BADEA98D1A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1EA5CB-38A9-4B0C-A624-4252D6733CE7}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="13_ncr:1_{C1AEC928-3B3E-6A48-BC07-BADEA98D1A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F5590A4-3B23-4E28-B28D-64EB35E306A5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Fundamentals" sheetId="10" r:id="rId2"/>
     <sheet name="Schema &lt;table_name&gt;" sheetId="3" r:id="rId3"/>
     <sheet name="Relationships" sheetId="23" r:id="rId4"/>
-    <sheet name="Enum" sheetId="26" r:id="rId5"/>
+    <sheet name="Enums" sheetId="26" r:id="rId5"/>
     <sheet name="Synonyms" sheetId="27" r:id="rId6"/>
     <sheet name="Verified Statements" sheetId="28" r:id="rId7"/>
     <sheet name="Constraints" sheetId="29" r:id="rId8"/>
@@ -47,7 +47,7 @@
     <definedName name="description.purpose">Fundamentals!$C$19</definedName>
     <definedName name="description.usage">Fundamentals!$C$21</definedName>
     <definedName name="domain">Fundamentals!$C$14</definedName>
-    <definedName name="enum">Enum!$A$4:$Z$1000</definedName>
+    <definedName name="enum">Enums!$A$4:$Z$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
@@ -68,7 +68,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$18:$AZ$981</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AZ$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="242">
   <si>
     <t>Open Data Contract Standard V3</t>
   </si>
@@ -269,7 +269,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>Context Instructions</t>
+    <t>Context (Guidance for AI)</t>
   </si>
   <si>
     <t>Schema</t>
@@ -299,15 +299,12 @@
     <t>Deprecated</t>
   </si>
   <si>
-    <t>Custom Property</t>
-  </si>
-  <si>
-    <t>Custom Value</t>
-  </si>
-  <si>
     <t>Logical Type Options</t>
   </si>
   <si>
+    <t>Custom Properties (add as needed)</t>
+  </si>
+  <si>
     <t>Property</t>
   </si>
   <si>
@@ -329,6 +326,9 @@
     <t>Classification</t>
   </si>
   <si>
+    <t>Semantic Type</t>
+  </si>
+  <si>
     <t>Authoritative Definition URL</t>
   </si>
   <si>
@@ -407,9 +407,6 @@
     <t>Pattern</t>
   </si>
   <si>
-    <t>Semantic Type</t>
-  </si>
-  <si>
     <t>Comments (internal)</t>
   </si>
   <si>
@@ -431,10 +428,10 @@
     <t>To</t>
   </si>
   <si>
-    <t>Enum</t>
-  </si>
-  <si>
-    <t>Allowed values of a property. Use schema.property dot syntax for the property (e.g. orders.status).</t>
+    <t>Enums</t>
+  </si>
+  <si>
+    <t>Restrict the allowed values of a property. Use one row per accepted value.</t>
   </si>
   <si>
     <t>Value</t>
@@ -482,7 +479,7 @@
     <t>Quality</t>
   </si>
   <si>
-    <t>This section describes data quality rules &amp; parameters. They are tightly linked to the schema described in the previous sheet(s).</t>
+    <t>Add quality rules to the schemas of the contract or their properties.</t>
   </si>
   <si>
     <t>Quality Type</t>
@@ -708,7 +705,7 @@
     <t>Custom Properties</t>
   </si>
   <si>
-    <t>This section covers custom properties you may find in a data contract.</t>
+    <t>Store additional information about the contract or specific elements of it. This is more fine-grained than the columns for Custom Properties on other sheets.</t>
   </si>
   <si>
     <t>Element Type</t>
@@ -1084,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1166,6 +1163,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1184,7 +1182,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1205,9 +1211,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1904,7 +1914,7 @@
       <c r="A27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="33" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="13"/>
@@ -1975,192 +1985,268 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB3633-F435-1B44-A99B-F400ACF77C57}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
     <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
     <col min="4" max="6" width="23.7109375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="28.5703125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="7" width="28.5703125" style="2" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24">
+    <row r="1" spans="1:10" ht="24">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75">
+      <c r="A2" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:10" ht="15.95" customHeight="1">
+      <c r="H3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" s="9" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D4" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>131</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="B5:F61" xr:uid="{19A11CF7-5A67-E844-8CDE-E9312B26965E}"/>
   </dataValidations>
@@ -2170,53 +2256,61 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
     <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
     <col min="4" max="7" width="23.7109375" style="2" customWidth="1"/>
-    <col min="8" max="10" width="28.5703125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="2"/>
+    <col min="8" max="8" width="28.5703125" style="2" customWidth="1"/>
+    <col min="9" max="11" width="26.7109375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24">
+    <row r="1" spans="1:11" ht="24">
       <c r="A1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+    <row r="4" spans="1:11" ht="15.75">
+      <c r="A4" s="7" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75">
+      <c r="A5" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75">
+      <c r="A6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75">
+      <c r="A7" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.95" customHeight="1">
+      <c r="I8" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75">
+      <c r="A9" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="B7" s="5"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75">
-      <c r="A9" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>32</v>
@@ -2225,28 +2319,25 @@
         <v>39</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>142</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2254,8 +2345,12 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2263,8 +2358,12 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2272,8 +2371,12 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2281,8 +2384,12 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2290,8 +2397,12 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2299,8 +2410,12 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2308,8 +2423,12 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2317,8 +2436,12 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2326,8 +2449,12 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2335,8 +2462,12 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2344,8 +2475,12 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2353,8 +2488,12 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2362,8 +2501,12 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2371,8 +2514,12 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2380,8 +2527,12 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2389,8 +2540,12 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2398,8 +2553,15 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I8:K8"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="B10:G66" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
   </dataValidations>
@@ -2409,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
@@ -2417,166 +2579,242 @@
     <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" style="2" customWidth="1"/>
-    <col min="6" max="8" width="28.5703125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="6" max="6" width="28.5703125" style="2" customWidth="1"/>
+    <col min="7" max="9" width="26.7109375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24">
+    <row r="1" spans="1:9" ht="24">
       <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75">
+      <c r="A2" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="3" spans="1:9" ht="15.95" customHeight="1">
+      <c r="G3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" sqref="B5:E61" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
   </dataValidations>
@@ -2586,7 +2824,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C18618-CA09-244F-9E12-D5D128AED5CE}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
@@ -2594,195 +2832,271 @@
     <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
     <col min="4" max="5" width="32.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="34.7109375" style="2" customWidth="1"/>
-    <col min="7" max="9" width="28.5703125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="7" width="28.5703125" style="2" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24">
+    <row r="1" spans="1:10" ht="24">
       <c r="A1" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" s="7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.95" customHeight="1">
+      <c r="H5" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="26"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H5:J5"/>
+  </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="1" sqref="B7:F63" xr:uid="{7F4EE529-7BE7-6547-817C-8DBC88D35FEC}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="B4" xr:uid="{8220F424-DC29-F648-BD41-E75C77AE8B05}"/>
@@ -2807,19 +3121,19 @@
   <sheetData>
     <row r="1" spans="1:26" ht="24">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B2" s="4"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="5"/>
@@ -2829,7 +3143,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5"/>
@@ -2863,12 +3177,12 @@
     </row>
     <row r="10" spans="1:26" ht="15.75">
       <c r="A10" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75">
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2897,7 +3211,7 @@
     </row>
     <row r="12" spans="1:26" ht="15.75">
       <c r="B12" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -2926,7 +3240,7 @@
     </row>
     <row r="13" spans="1:26" ht="15.75">
       <c r="B13" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -2955,7 +3269,7 @@
     </row>
     <row r="14" spans="1:26" ht="15.75">
       <c r="B14" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2984,7 +3298,7 @@
     </row>
     <row r="15" spans="1:26" ht="15.75">
       <c r="B15" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -3013,7 +3327,7 @@
     </row>
     <row r="16" spans="1:26" ht="15.75">
       <c r="B16" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -3042,7 +3356,7 @@
     </row>
     <row r="17" spans="2:26" ht="15.75">
       <c r="B17" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -3071,7 +3385,7 @@
     </row>
     <row r="18" spans="2:26" ht="15.75">
       <c r="B18" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -3129,7 +3443,7 @@
     </row>
     <row r="20" spans="2:26" ht="15.75">
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -3158,7 +3472,7 @@
     </row>
     <row r="21" spans="2:26" ht="15.75">
       <c r="B21" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -3187,7 +3501,7 @@
     </row>
     <row r="22" spans="2:26" ht="15.75">
       <c r="B22" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -3216,7 +3530,7 @@
     </row>
     <row r="23" spans="2:26" ht="15.75">
       <c r="B23" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -3245,7 +3559,7 @@
     </row>
     <row r="24" spans="2:26" ht="15.75">
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -3274,7 +3588,7 @@
     </row>
     <row r="25" spans="2:26" ht="15.75">
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -3303,7 +3617,7 @@
     </row>
     <row r="26" spans="2:26" ht="15.75">
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -3332,7 +3646,7 @@
     </row>
     <row r="27" spans="2:26" ht="15.75">
       <c r="B27" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3390,7 +3704,7 @@
     </row>
     <row r="29" spans="2:26" ht="15.75">
       <c r="B29" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3419,7 +3733,7 @@
     </row>
     <row r="30" spans="2:26" ht="15.75">
       <c r="B30" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3448,7 +3762,7 @@
     </row>
     <row r="31" spans="2:26" ht="15.75">
       <c r="B31" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -3477,7 +3791,7 @@
     </row>
     <row r="32" spans="2:26" ht="15.75">
       <c r="B32" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3504,9 +3818,9 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="2:26" ht="15.75">
+    <row r="33" spans="1:26" ht="15.75">
       <c r="B33" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3533,8 +3847,8 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="2:26" ht="15.75"/>
-    <row r="35" spans="2:26" ht="15.75">
+    <row r="34" spans="1:26" ht="15.75"/>
+    <row r="35" spans="1:26" ht="15.75">
       <c r="B35" s="2" t="s">
         <v>31</v>
       </c>
@@ -3563,39 +3877,12 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="2:26" ht="15.75">
-      <c r="B36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
-      <c r="V36" s="5"/>
-      <c r="W36" s="5"/>
-      <c r="X36" s="5"/>
-      <c r="Y36" s="5"/>
-      <c r="Z36" s="5"/>
-    </row>
-    <row r="37" spans="2:26" ht="15.75">
-      <c r="B37" s="2" t="s">
+    <row r="36" spans="1:26" ht="15.75">
+      <c r="A36" s="7" t="s">
         <v>55</v>
       </c>
+    </row>
+    <row r="37" spans="1:26" ht="15.75">
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -3621,17 +3908,67 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" spans="2:26" ht="15.75"/>
-    <row r="39" spans="2:26" ht="15.75"/>
-    <row r="40" spans="2:26" ht="15.75"/>
-    <row r="41" spans="2:26" ht="15.75"/>
-    <row r="42" spans="2:26" ht="15.75"/>
-    <row r="43" spans="2:26" ht="15.75"/>
-    <row r="44" spans="2:26" ht="15.75"/>
-    <row r="45" spans="2:26" ht="15.75"/>
-    <row r="46" spans="2:26" ht="15.75"/>
-    <row r="47" spans="2:26" ht="15.75"/>
-    <row r="48" spans="2:26" ht="15.75"/>
+    <row r="38" spans="1:26" ht="15.75">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+    </row>
+    <row r="39" spans="1:26" ht="15.75">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+    </row>
+    <row r="40" spans="1:26" ht="15.75"/>
+    <row r="41" spans="1:26" ht="15.75"/>
+    <row r="42" spans="1:26" ht="15.75"/>
+    <row r="43" spans="1:26" ht="15.75"/>
+    <row r="44" spans="1:26" ht="15.75"/>
+    <row r="45" spans="1:26" ht="15.75"/>
+    <row r="46" spans="1:26" ht="15.75"/>
+    <row r="47" spans="1:26" ht="15.75"/>
+    <row r="48" spans="1:26" ht="15.75"/>
     <row r="49" ht="15.75"/>
     <row r="50" ht="15.75"/>
     <row r="51" ht="15.75"/>
@@ -3671,8 +4008,13 @@
     <row r="85" ht="15.75"/>
   </sheetData>
   <conditionalFormatting sqref="C11:Z33">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:Z39">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B37,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -3697,30 +4039,30 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" ht="24">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A2" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="2" customFormat="1" ht="15.95"/>
     <row r="4" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A4" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A5" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A6" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B6" s="5"/>
     </row>
@@ -3749,26 +4091,26 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>48</v>
@@ -3777,7 +4119,7 @@
         <v>39</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>31</v>
@@ -3785,11 +4127,11 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="5" t="str">
         <f>IF(owner &lt;&gt; "", owner, "")</f>
@@ -3987,23 +4329,23 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>48</v>
@@ -4171,341 +4513,341 @@
   <sheetData>
     <row r="1" spans="1:45">
       <c r="A1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" t="s">
         <v>196</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>197</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>198</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>199</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>200</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>201</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>202</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>203</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>204</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>205</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>206</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>207</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>208</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>209</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>210</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>211</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>212</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>213</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>214</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>215</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>216</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>217</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>218</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>219</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>220</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>221</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>222</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>223</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>224</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>225</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>226</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>227</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>228</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>229</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>230</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>231</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>232</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>233</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>234</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>235</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>236</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>237</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>238</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>239</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG2" t="s">
         <v>241</v>
       </c>
-      <c r="AG2" t="s">
-        <v>242</v>
-      </c>
       <c r="AJ2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS2" t="s">
         <v>241</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:45">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H3" t="s">
+        <v>240</v>
+      </c>
+      <c r="S3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE3" t="s">
         <v>241</v>
       </c>
-      <c r="S3" t="s">
+      <c r="AN3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS3" t="s">
         <v>241</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>242</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:45">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:45">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I5" t="s">
         <v>241</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N5" t="s">
+        <v>240</v>
+      </c>
+      <c r="O5" t="s">
         <v>241</v>
       </c>
-      <c r="I5" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>240</v>
+      </c>
+      <c r="R5" t="s">
+        <v>240</v>
+      </c>
+      <c r="T5" t="s">
+        <v>240</v>
+      </c>
+      <c r="U5" t="s">
+        <v>240</v>
+      </c>
+      <c r="V5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM5" t="s">
         <v>241</v>
       </c>
-      <c r="M5" t="s">
+      <c r="AO5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS5" t="s">
         <v>241</v>
-      </c>
-      <c r="N5" t="s">
-        <v>241</v>
-      </c>
-      <c r="O5" t="s">
-        <v>242</v>
-      </c>
-      <c r="P5" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>241</v>
-      </c>
-      <c r="R5" t="s">
-        <v>241</v>
-      </c>
-      <c r="T5" t="s">
-        <v>241</v>
-      </c>
-      <c r="U5" t="s">
-        <v>241</v>
-      </c>
-      <c r="V5" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:45">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS6" t="s">
         <v>241</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:45">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AH7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AI7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:45">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Y8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AH8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AI8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:45">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AH9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:45">
@@ -4513,299 +4855,299 @@
         <v>78</v>
       </c>
       <c r="D10" t="s">
+        <v>240</v>
+      </c>
+      <c r="N10" t="s">
         <v>241</v>
       </c>
-      <c r="N10" t="s">
-        <v>242</v>
-      </c>
       <c r="W10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Y10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AH10" t="s">
         <v>241</v>
       </c>
-      <c r="AH10" t="s">
-        <v>242</v>
-      </c>
       <c r="AI10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:45">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" t="s">
+        <v>240</v>
+      </c>
+      <c r="H11" t="s">
         <v>241</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J11" t="s">
+        <v>240</v>
+      </c>
+      <c r="L11" t="s">
+        <v>240</v>
+      </c>
+      <c r="M11" t="s">
         <v>241</v>
       </c>
-      <c r="H11" t="s">
-        <v>242</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="O11" t="s">
+        <v>240</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R11" t="s">
+        <v>240</v>
+      </c>
+      <c r="T11" t="s">
+        <v>240</v>
+      </c>
+      <c r="U11" t="s">
+        <v>240</v>
+      </c>
+      <c r="V11" t="s">
+        <v>240</v>
+      </c>
+      <c r="W11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB11" t="s">
         <v>241</v>
       </c>
-      <c r="J11" t="s">
+      <c r="AC11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG11" t="s">
         <v>241</v>
       </c>
-      <c r="L11" t="s">
+      <c r="AJ11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP11" t="s">
         <v>241</v>
       </c>
-      <c r="M11" t="s">
-        <v>242</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="AQ11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS11" t="s">
         <v>241</v>
-      </c>
-      <c r="P11" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>241</v>
-      </c>
-      <c r="R11" t="s">
-        <v>241</v>
-      </c>
-      <c r="T11" t="s">
-        <v>241</v>
-      </c>
-      <c r="U11" t="s">
-        <v>241</v>
-      </c>
-      <c r="V11" t="s">
-        <v>241</v>
-      </c>
-      <c r="W11" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>242</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>242</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:45">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>240</v>
+      </c>
+      <c r="N12" t="s">
         <v>241</v>
       </c>
-      <c r="D12" t="s">
+      <c r="AH12" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS12" t="s">
         <v>241</v>
-      </c>
-      <c r="N12" t="s">
-        <v>242</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>241</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:45">
       <c r="A13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:45">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS14" t="s">
         <v>241</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:45">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G15" t="s">
+        <v>240</v>
+      </c>
+      <c r="I15" t="s">
+        <v>240</v>
+      </c>
+      <c r="J15" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" t="s">
         <v>241</v>
       </c>
-      <c r="I15" t="s">
+      <c r="M15" t="s">
         <v>241</v>
       </c>
-      <c r="J15" t="s">
+      <c r="O15" t="s">
         <v>241</v>
       </c>
-      <c r="L15" t="s">
-        <v>242</v>
-      </c>
-      <c r="M15" t="s">
-        <v>242</v>
-      </c>
-      <c r="O15" t="s">
-        <v>242</v>
-      </c>
       <c r="P15" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>240</v>
+      </c>
+      <c r="R15" t="s">
         <v>241</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="T15" t="s">
         <v>241</v>
       </c>
-      <c r="R15" t="s">
-        <v>242</v>
-      </c>
-      <c r="T15" t="s">
-        <v>242</v>
-      </c>
       <c r="U15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB15" t="s">
         <v>241</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AC15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK15" t="s">
         <v>241</v>
       </c>
-      <c r="AB15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC15" t="s">
+      <c r="AL15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM15" t="s">
         <v>241</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AN15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AO15" t="s">
         <v>241</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AP15" t="s">
         <v>241</v>
       </c>
-      <c r="AK15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AL15" t="s">
+      <c r="AQ15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR15" t="s">
         <v>241</v>
       </c>
-      <c r="AM15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AN15" t="s">
+      <c r="AS15" t="s">
         <v>241</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>241</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>242</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:45">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS16" t="s">
         <v>241</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:45">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="X17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:45">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:45">
@@ -4813,110 +5155,110 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
+        <v>240</v>
+      </c>
+      <c r="H19" t="s">
+        <v>240</v>
+      </c>
+      <c r="J19" t="s">
         <v>241</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
         <v>241</v>
       </c>
-      <c r="J19" t="s">
-        <v>242</v>
-      </c>
-      <c r="K19" t="s">
-        <v>242</v>
-      </c>
       <c r="L19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P19" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q19" t="s">
         <v>241</v>
       </c>
-      <c r="Q19" t="s">
-        <v>242</v>
-      </c>
       <c r="AC19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE19" t="s">
         <v>241</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AG19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS19" t="s">
         <v>241</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>242</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:45">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA20" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS20" t="s">
         <v>241</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:45">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AS21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:45">
       <c r="A22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X22" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS22" t="s">
         <v>241</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:45">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ23" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS23" t="s">
         <v>241</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:45">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5008,10 +5350,10 @@
       <c r="B11" s="7"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="5"/>
       <c r="E12" s="6"/>
     </row>
@@ -5111,8 +5453,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AQ54"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <dimension ref="A1:AR54"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="24" style="2" bestFit="1" customWidth="1"/>
@@ -5122,298 +5464,378 @@
     <col min="6" max="6" width="35.7109375" style="2" customWidth="1"/>
     <col min="7" max="8" width="10" style="2" customWidth="1"/>
     <col min="9" max="9" width="14.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="28.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="19" style="2" customWidth="1"/>
-    <col min="21" max="21" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="37" width="15.42578125" style="2" customWidth="1"/>
-    <col min="38" max="43" width="28.5703125" style="2" customWidth="1"/>
-    <col min="44" max="16384" width="8.85546875" style="2"/>
+    <col min="10" max="11" width="21" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.7109375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="19" style="2" customWidth="1"/>
+    <col min="23" max="23" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="39" width="15.42578125" style="2" customWidth="1"/>
+    <col min="40" max="40" width="21" style="2" customWidth="1"/>
+    <col min="41" max="41" width="28.5703125" style="2" customWidth="1"/>
+    <col min="42" max="44" width="26.7109375" style="2" customWidth="1"/>
+    <col min="45" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24">
+    <row r="1" spans="1:44" ht="24">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:44">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:44">
       <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:44">
       <c r="A5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6" spans="1:44">
       <c r="A6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+    </row>
+    <row r="7" spans="1:44">
       <c r="A7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+    </row>
+    <row r="8" spans="1:44">
       <c r="A8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="39"/>
+    </row>
+    <row r="9" spans="1:44">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+    </row>
+    <row r="10" spans="1:44">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.75">
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+    </row>
+    <row r="11" spans="1:44">
       <c r="A11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75">
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12" spans="1:44">
       <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.75">
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45"/>
+    </row>
+    <row r="13" spans="1:44">
       <c r="A13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75">
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
+    </row>
+    <row r="14" spans="1:44">
       <c r="A14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75">
-      <c r="A15" s="7" t="s">
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="45"/>
+    </row>
+    <row r="15" spans="1:44">
+      <c r="Y15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.75">
-      <c r="A16" s="7" t="s">
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="20"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="20"/>
+      <c r="AM15" s="21"/>
+      <c r="AN15" s="40"/>
+      <c r="AP15" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42"/>
-    </row>
-    <row r="17" spans="1:43" ht="15.75">
-      <c r="W17" s="19" t="s">
+      <c r="AQ15" s="42"/>
+      <c r="AR15" s="42"/>
+    </row>
+    <row r="16" spans="1:44">
+      <c r="A16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
-      <c r="AE17" s="20"/>
-      <c r="AF17" s="20"/>
-      <c r="AG17" s="20"/>
-      <c r="AH17" s="20"/>
-      <c r="AI17" s="20"/>
-      <c r="AJ17" s="20"/>
-      <c r="AK17" s="21"/>
-    </row>
-    <row r="18" spans="1:43" ht="15.75">
-      <c r="A18" s="9" t="s">
+      <c r="B16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="D16" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="F16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="10" t="s">
+      <c r="H16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="I16" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="J16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="L16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="N16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="O16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="P16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="Q16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="R16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Q18" s="10" t="s">
+      <c r="S16" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="R18" s="10" t="s">
+      <c r="T16" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="S18" s="10" t="s">
+      <c r="U16" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="T18" s="10" t="s">
+      <c r="V16" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="U18" s="10" t="s">
+      <c r="W16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="V18" s="10" t="s">
+      <c r="X16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="W18" s="10" t="s">
+      <c r="Y16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="X18" s="10" t="s">
+      <c r="Z16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="Y18" s="10" t="s">
+      <c r="AA16" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="Z18" s="10" t="s">
+      <c r="AB16" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="AA18" s="10" t="s">
+      <c r="AC16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AB18" s="10" t="s">
+      <c r="AD16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AC18" s="10" t="s">
+      <c r="AE16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AD18" s="10" t="s">
+      <c r="AF16" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="AE18" s="10" t="s">
+      <c r="AG16" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AF18" s="10" t="s">
+      <c r="AH16" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AG18" s="10" t="s">
+      <c r="AI16" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AH18" s="10" t="s">
+      <c r="AJ16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AI18" s="10" t="s">
+      <c r="AK16" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="AJ18" s="10" t="s">
+      <c r="AL16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AK18" s="10" t="s">
+      <c r="AM16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="AL18" s="9" t="s">
+      <c r="AN16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO16" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AM18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN18" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AO18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AP18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ18" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:43" ht="15.75">
+      <c r="AP16" s="9"/>
+      <c r="AQ16" s="9"/>
+      <c r="AR16" s="9"/>
+    </row>
+    <row r="17" spans="1:44">
+      <c r="A17" s="17"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="15"/>
+      <c r="AK17" s="15"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="15"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44">
+      <c r="A18" s="17"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="15"/>
+      <c r="AF18" s="15"/>
+      <c r="AG18" s="15"/>
+      <c r="AH18" s="15"/>
+      <c r="AI18" s="15"/>
+      <c r="AJ18" s="15"/>
+      <c r="AK18" s="15"/>
+      <c r="AL18" s="15"/>
+      <c r="AM18" s="15"/>
+      <c r="AN18" s="15"/>
+      <c r="AO18" s="15"/>
+      <c r="AP18" s="15"/>
+      <c r="AQ18" s="15"/>
+      <c r="AR18" s="15"/>
+    </row>
+    <row r="19" spans="1:44">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -5457,8 +5879,9 @@
       <c r="AO19" s="15"/>
       <c r="AP19" s="15"/>
       <c r="AQ19" s="15"/>
-    </row>
-    <row r="20" spans="1:43" ht="15.75">
+      <c r="AR19" s="15"/>
+    </row>
+    <row r="20" spans="1:44">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -5502,8 +5925,9 @@
       <c r="AO20" s="15"/>
       <c r="AP20" s="15"/>
       <c r="AQ20" s="15"/>
-    </row>
-    <row r="21" spans="1:43" ht="15.75">
+      <c r="AR20" s="15"/>
+    </row>
+    <row r="21" spans="1:44">
       <c r="A21" s="17"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -5547,8 +5971,9 @@
       <c r="AO21" s="15"/>
       <c r="AP21" s="15"/>
       <c r="AQ21" s="15"/>
-    </row>
-    <row r="22" spans="1:43" ht="15.75">
+      <c r="AR21" s="15"/>
+    </row>
+    <row r="22" spans="1:44">
       <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -5592,8 +6017,9 @@
       <c r="AO22" s="15"/>
       <c r="AP22" s="15"/>
       <c r="AQ22" s="15"/>
-    </row>
-    <row r="23" spans="1:43" ht="15.75">
+      <c r="AR22" s="15"/>
+    </row>
+    <row r="23" spans="1:44">
       <c r="A23" s="17"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -5637,9 +6063,10 @@
       <c r="AO23" s="15"/>
       <c r="AP23" s="15"/>
       <c r="AQ23" s="15"/>
-    </row>
-    <row r="24" spans="1:43" ht="15.75">
-      <c r="A24" s="17"/>
+      <c r="AR23" s="15"/>
+    </row>
+    <row r="24" spans="1:44">
+      <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -5682,9 +6109,10 @@
       <c r="AO24" s="15"/>
       <c r="AP24" s="15"/>
       <c r="AQ24" s="15"/>
-    </row>
-    <row r="25" spans="1:43" ht="15.75">
-      <c r="A25" s="17"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44">
+      <c r="A25" s="18"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -5727,8 +6155,9 @@
       <c r="AO25" s="15"/>
       <c r="AP25" s="15"/>
       <c r="AQ25" s="15"/>
-    </row>
-    <row r="26" spans="1:43" ht="15.75">
+      <c r="AR25" s="15"/>
+    </row>
+    <row r="26" spans="1:44">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -5772,9 +6201,10 @@
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
-    </row>
-    <row r="27" spans="1:43" ht="15.75">
-      <c r="A27" s="18"/>
+      <c r="AR26" s="15"/>
+    </row>
+    <row r="27" spans="1:44">
+      <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -5817,9 +6247,10 @@
       <c r="AO27" s="15"/>
       <c r="AP27" s="15"/>
       <c r="AQ27" s="15"/>
-    </row>
-    <row r="28" spans="1:43" ht="15.75">
-      <c r="A28" s="18"/>
+      <c r="AR27" s="15"/>
+    </row>
+    <row r="28" spans="1:44">
+      <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
@@ -5862,8 +6293,9 @@
       <c r="AO28" s="15"/>
       <c r="AP28" s="15"/>
       <c r="AQ28" s="15"/>
-    </row>
-    <row r="29" spans="1:43" ht="15.75">
+      <c r="AR28" s="15"/>
+    </row>
+    <row r="29" spans="1:44">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -5907,8 +6339,9 @@
       <c r="AO29" s="15"/>
       <c r="AP29" s="15"/>
       <c r="AQ29" s="15"/>
-    </row>
-    <row r="30" spans="1:43" ht="15.75">
+      <c r="AR29" s="15"/>
+    </row>
+    <row r="30" spans="1:44">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -5952,8 +6385,9 @@
       <c r="AO30" s="15"/>
       <c r="AP30" s="15"/>
       <c r="AQ30" s="15"/>
-    </row>
-    <row r="31" spans="1:43" ht="15.75">
+      <c r="AR30" s="15"/>
+    </row>
+    <row r="31" spans="1:44">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -5997,8 +6431,9 @@
       <c r="AO31" s="15"/>
       <c r="AP31" s="15"/>
       <c r="AQ31" s="15"/>
-    </row>
-    <row r="32" spans="1:43" ht="15.75">
+      <c r="AR31" s="15"/>
+    </row>
+    <row r="32" spans="1:44">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -6042,8 +6477,9 @@
       <c r="AO32" s="15"/>
       <c r="AP32" s="15"/>
       <c r="AQ32" s="15"/>
-    </row>
-    <row r="33" spans="1:43" ht="15.75">
+      <c r="AR32" s="15"/>
+    </row>
+    <row r="33" spans="1:44">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -6087,8 +6523,9 @@
       <c r="AO33" s="15"/>
       <c r="AP33" s="15"/>
       <c r="AQ33" s="15"/>
-    </row>
-    <row r="34" spans="1:43" ht="15.75">
+      <c r="AR33" s="15"/>
+    </row>
+    <row r="34" spans="1:44">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -6132,8 +6569,9 @@
       <c r="AO34" s="15"/>
       <c r="AP34" s="15"/>
       <c r="AQ34" s="15"/>
-    </row>
-    <row r="35" spans="1:43" ht="15.75">
+      <c r="AR34" s="15"/>
+    </row>
+    <row r="35" spans="1:44">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -6177,8 +6615,9 @@
       <c r="AO35" s="15"/>
       <c r="AP35" s="15"/>
       <c r="AQ35" s="15"/>
-    </row>
-    <row r="36" spans="1:43" ht="15.75">
+      <c r="AR35" s="15"/>
+    </row>
+    <row r="36" spans="1:44">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -6222,8 +6661,9 @@
       <c r="AO36" s="15"/>
       <c r="AP36" s="15"/>
       <c r="AQ36" s="15"/>
-    </row>
-    <row r="37" spans="1:43" ht="15.75">
+      <c r="AR36" s="15"/>
+    </row>
+    <row r="37" spans="1:44">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -6267,8 +6707,9 @@
       <c r="AO37" s="15"/>
       <c r="AP37" s="15"/>
       <c r="AQ37" s="15"/>
-    </row>
-    <row r="38" spans="1:43" ht="15.75">
+      <c r="AR37" s="15"/>
+    </row>
+    <row r="38" spans="1:44">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -6312,8 +6753,9 @@
       <c r="AO38" s="15"/>
       <c r="AP38" s="15"/>
       <c r="AQ38" s="15"/>
-    </row>
-    <row r="39" spans="1:43" ht="15.75">
+      <c r="AR38" s="15"/>
+    </row>
+    <row r="39" spans="1:44">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -6357,8 +6799,9 @@
       <c r="AO39" s="15"/>
       <c r="AP39" s="15"/>
       <c r="AQ39" s="15"/>
-    </row>
-    <row r="40" spans="1:43" ht="15.75">
+      <c r="AR39" s="15"/>
+    </row>
+    <row r="40" spans="1:44">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -6402,8 +6845,9 @@
       <c r="AO40" s="15"/>
       <c r="AP40" s="15"/>
       <c r="AQ40" s="15"/>
-    </row>
-    <row r="41" spans="1:43" ht="15.75">
+      <c r="AR40" s="15"/>
+    </row>
+    <row r="41" spans="1:44">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -6447,8 +6891,9 @@
       <c r="AO41" s="15"/>
       <c r="AP41" s="15"/>
       <c r="AQ41" s="15"/>
-    </row>
-    <row r="42" spans="1:43" ht="15.75">
+      <c r="AR41" s="15"/>
+    </row>
+    <row r="42" spans="1:44">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -6492,8 +6937,9 @@
       <c r="AO42" s="15"/>
       <c r="AP42" s="15"/>
       <c r="AQ42" s="15"/>
-    </row>
-    <row r="43" spans="1:43" ht="15.75">
+      <c r="AR42" s="15"/>
+    </row>
+    <row r="43" spans="1:44">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -6537,8 +6983,9 @@
       <c r="AO43" s="15"/>
       <c r="AP43" s="15"/>
       <c r="AQ43" s="15"/>
-    </row>
-    <row r="44" spans="1:43" ht="15.75">
+      <c r="AR43" s="15"/>
+    </row>
+    <row r="44" spans="1:44">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -6582,8 +7029,9 @@
       <c r="AO44" s="15"/>
       <c r="AP44" s="15"/>
       <c r="AQ44" s="15"/>
-    </row>
-    <row r="45" spans="1:43" ht="15.75">
+      <c r="AR44" s="15"/>
+    </row>
+    <row r="45" spans="1:44">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -6627,8 +7075,9 @@
       <c r="AO45" s="15"/>
       <c r="AP45" s="15"/>
       <c r="AQ45" s="15"/>
-    </row>
-    <row r="46" spans="1:43" ht="15.75">
+      <c r="AR45" s="15"/>
+    </row>
+    <row r="46" spans="1:44">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -6672,8 +7121,9 @@
       <c r="AO46" s="15"/>
       <c r="AP46" s="15"/>
       <c r="AQ46" s="15"/>
-    </row>
-    <row r="47" spans="1:43" ht="15.75">
+      <c r="AR46" s="15"/>
+    </row>
+    <row r="47" spans="1:44">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -6717,8 +7167,9 @@
       <c r="AO47" s="15"/>
       <c r="AP47" s="15"/>
       <c r="AQ47" s="15"/>
-    </row>
-    <row r="48" spans="1:43" ht="15.75">
+      <c r="AR47" s="15"/>
+    </row>
+    <row r="48" spans="1:44">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -6762,8 +7213,9 @@
       <c r="AO48" s="15"/>
       <c r="AP48" s="15"/>
       <c r="AQ48" s="15"/>
-    </row>
-    <row r="49" spans="1:43" ht="15.75">
+      <c r="AR48" s="15"/>
+    </row>
+    <row r="49" spans="1:44">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -6807,8 +7259,9 @@
       <c r="AO49" s="15"/>
       <c r="AP49" s="15"/>
       <c r="AQ49" s="15"/>
-    </row>
-    <row r="50" spans="1:43" ht="15.75">
+      <c r="AR49" s="15"/>
+    </row>
+    <row r="50" spans="1:44">
       <c r="A50" s="17"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -6852,8 +7305,9 @@
       <c r="AO50" s="15"/>
       <c r="AP50" s="15"/>
       <c r="AQ50" s="15"/>
-    </row>
-    <row r="51" spans="1:43" ht="15.75">
+      <c r="AR50" s="15"/>
+    </row>
+    <row r="51" spans="1:44">
       <c r="A51" s="17"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -6897,8 +7351,9 @@
       <c r="AO51" s="15"/>
       <c r="AP51" s="15"/>
       <c r="AQ51" s="15"/>
-    </row>
-    <row r="52" spans="1:43" ht="15.75">
+      <c r="AR51" s="15"/>
+    </row>
+    <row r="52" spans="1:44">
       <c r="A52" s="17"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -6942,99 +7397,16 @@
       <c r="AO52" s="15"/>
       <c r="AP52" s="15"/>
       <c r="AQ52" s="15"/>
-    </row>
-    <row r="53" spans="1:43" ht="15.75">
-      <c r="A53" s="17"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="15"/>
-      <c r="S53" s="15"/>
-      <c r="T53" s="15"/>
-      <c r="U53" s="15"/>
-      <c r="V53" s="15"/>
-      <c r="W53" s="15"/>
-      <c r="X53" s="15"/>
-      <c r="Y53" s="15"/>
-      <c r="Z53" s="15"/>
-      <c r="AA53" s="15"/>
-      <c r="AB53" s="15"/>
-      <c r="AC53" s="15"/>
-      <c r="AD53" s="15"/>
-      <c r="AE53" s="15"/>
-      <c r="AF53" s="15"/>
-      <c r="AG53" s="15"/>
-      <c r="AH53" s="15"/>
-      <c r="AI53" s="15"/>
-      <c r="AJ53" s="15"/>
-      <c r="AK53" s="15"/>
-      <c r="AL53" s="15"/>
-      <c r="AM53" s="15"/>
-      <c r="AN53" s="15"/>
-      <c r="AO53" s="15"/>
-      <c r="AP53" s="15"/>
-      <c r="AQ53" s="15"/>
-    </row>
-    <row r="54" spans="1:43" ht="15.75">
-      <c r="A54" s="17"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="15"/>
-      <c r="S54" s="15"/>
-      <c r="T54" s="15"/>
-      <c r="U54" s="15"/>
-      <c r="V54" s="15"/>
-      <c r="W54" s="15"/>
-      <c r="X54" s="15"/>
-      <c r="Y54" s="15"/>
-      <c r="Z54" s="15"/>
-      <c r="AA54" s="15"/>
-      <c r="AB54" s="15"/>
-      <c r="AC54" s="15"/>
-      <c r="AD54" s="15"/>
-      <c r="AE54" s="15"/>
-      <c r="AF54" s="15"/>
-      <c r="AG54" s="15"/>
-      <c r="AH54" s="15"/>
-      <c r="AI54" s="15"/>
-      <c r="AJ54" s="15"/>
-      <c r="AK54" s="15"/>
-      <c r="AL54" s="15"/>
-      <c r="AM54" s="15"/>
-      <c r="AN54" s="15"/>
-      <c r="AO54" s="15"/>
-      <c r="AP54" s="15"/>
-      <c r="AQ54" s="15"/>
-    </row>
+      <c r="AR52" s="15"/>
+    </row>
+    <row r="53" spans="1:44"/>
+    <row r="54" spans="1:44"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
@@ -7042,40 +7414,34 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
   </mergeCells>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H19:H54" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H17:H52" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B19:B54 J19:J54 M19:U54 W19:AK54" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G19:G54" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
+    <dataValidation allowBlank="1" sqref="B17:B52 L17:L52 O17:W52 Y17:AN52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Schema Name" prompt="The name of the schema (e.g., table) must match the Sheet name &quot;Schema &lt;schema_name&gt;&quot;" sqref="B5:E5" xr:uid="{8B3F718D-6361-B845-86DC-2F310C7348A9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A18" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="L19:L54" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A16" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="N17:N52" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
       <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I19:I54" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I52" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
       <formula1>"confidential,restricted,public"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="K19:K54" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
-    <dataValidation type="list" allowBlank="1" sqref="V19:V54" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="M17:M52" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
+    <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AL18" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 AM19:AM54" xr:uid="{5951D012-9713-4BF9-B49A-36D7824469E7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 J17:J52" xr:uid="{5951D012-9713-4BF9-B49A-36D7824469E7}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL19:AL54" xr:uid="{5C060A55-B19E-4700-8202-4FE63BD6E0A6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:K52" xr:uid="{5C060A55-B19E-4700-8202-4FE63BD6E0A6}">
       <formula1>"column,measure,dimension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C54" xr:uid="{BD7CBF6C-981D-40E3-9447-A74CA1C2780C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{BD7CBF6C-981D-40E3-9447-A74CA1C2780C}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7085,183 +7451,235 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C8C2B4-64D3-DB4C-BBDA-0F192B30B9A9}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="29" customWidth="1"/>
     <col min="2" max="2" width="13" style="29" customWidth="1"/>
     <col min="3" max="3" width="48.42578125" style="29" customWidth="1"/>
     <col min="4" max="4" width="42.85546875" style="29" customWidth="1"/>
-    <col min="5" max="7" width="28.5703125" style="29" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="29"/>
+    <col min="5" max="5" width="28.5703125" style="29" customWidth="1"/>
+    <col min="6" max="8" width="26.7109375" style="29" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24">
+    <row r="1" spans="1:8" ht="24">
       <c r="A1" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75">
+      <c r="A2" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="28"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="30" t="s">
+      <c r="B2" s="30"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="30"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="30" t="s">
+      <c r="B3" s="30"/>
+      <c r="F3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="31" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" s="30"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.75">
-      <c r="A4" s="31" t="s">
-        <v>95</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>48</v>
       </c>
       <c r="C4" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>96</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>97</v>
       </c>
       <c r="E4" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
-      <formula>C5="sql"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
   <dataValidations count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="A human-readable description of the relationship. Explain the business context or purpose of how the source and target are related." sqref="E4" xr:uid="{EE4A1054-F15A-664C-B875-762503081248}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Type" prompt="Type of the relationship column(s)." sqref="B4" xr:uid="{41A27CD9-820D-2E48-B8C9-300C785AF670}"/>
@@ -7283,296 +7701,57 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0086E894-DDEF-454E-BBEC-466C190BF33C}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="28.5703125" customWidth="1"/>
     <col min="5" max="5" width="47.5703125" customWidth="1"/>
-    <col min="6" max="9" width="28.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75">
-      <c r="A4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.75">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC387154-8B4D-4EA8-8294-5AF954FB5535}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="47.5703125" customWidth="1"/>
-    <col min="5" max="10" width="28.5703125" customWidth="1"/>
+    <col min="6" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>103</v>
-      </c>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75">
+      <c r="H3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="15.75">
       <c r="A4" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>105</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>55</v>
-      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="15.75">
       <c r="A5" s="5"/>
@@ -7779,57 +7958,71 @@
       <c r="J21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE481688-B3AC-4CED-871E-24F494244609}">
-  <dimension ref="A1:H21"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC387154-8B4D-4EA8-8294-5AF954FB5535}">
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="4" width="57.140625" customWidth="1"/>
+    <col min="1" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" customWidth="1"/>
     <col min="5" max="8" width="28.5703125" customWidth="1"/>
+    <col min="9" max="11" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1">
+    <row r="1" spans="1:11" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75">
+      <c r="I3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75">
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -7838,8 +8031,11 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -7848,8 +8044,11 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -7858,8 +8057,11 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -7868,8 +8070,11 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -7878,8 +8083,11 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75">
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -7888,8 +8096,11 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75">
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -7898,8 +8109,11 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.75">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -7908,8 +8122,11 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75">
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -7918,8 +8135,11 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75">
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -7928,8 +8148,11 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75">
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -7938,8 +8161,11 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75">
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -7948,8 +8174,11 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75">
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.75">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -7958,8 +8187,11 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75">
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -7968,8 +8200,11 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75">
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -7978,8 +8213,11 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75">
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -7988,8 +8226,11 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75">
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -7998,8 +8239,260 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE481688-B3AC-4CED-871E-24F494244609}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="4" width="57.140625" customWidth="1"/>
+    <col min="5" max="6" width="28.5703125" customWidth="1"/>
+    <col min="7" max="9" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75">
+      <c r="G3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{410BAB73-2EB0-4EA5-B7D4-D0794210AFC3}">
       <formula1>"Contract,Schema"</formula1>
@@ -8011,33 +8504,41 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FA52E6-D20E-4DFD-9B9D-0129E3657275}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="66.7109375" customWidth="1"/>
-    <col min="4" max="7" width="28.5703125" customWidth="1"/>
+    <col min="4" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="8" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" customHeight="1">
+    <row r="1" spans="1:8" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75">
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="F3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
       <c r="A4" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>43</v>
@@ -8045,14 +8546,11 @@
       <c r="E4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75">
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -8060,8 +8558,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -8069,8 +8568,9 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -8078,8 +8578,9 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.75">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -8087,8 +8588,9 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.75">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -8096,8 +8598,9 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.75">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -8105,8 +8608,9 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -8114,8 +8618,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -8123,8 +8628,9 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75">
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -8132,8 +8638,9 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -8141,8 +8648,9 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.75">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -8150,8 +8658,9 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -8159,8 +8668,9 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -8168,8 +8678,9 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -8177,8 +8688,9 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -8186,8 +8698,9 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -8195,8 +8708,9 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -8204,8 +8718,12 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{6C62E592-567C-4D75-BC42-BA79D40F91CF}">
       <formula1>"Contract,Schema"</formula1>
@@ -8217,7 +8735,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="29" customWidth="1"/>
@@ -8233,77 +8751,80 @@
     <col min="11" max="11" width="15.42578125" style="29" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" style="29" customWidth="1"/>
-    <col min="14" max="16" width="28.5703125" style="29" customWidth="1"/>
-    <col min="17" max="16384" width="8.85546875" style="29"/>
+    <col min="14" max="14" width="28.5703125" style="29" customWidth="1"/>
+    <col min="15" max="17" width="26.7109375" style="29" customWidth="1"/>
+    <col min="18" max="16384" width="8.85546875" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24">
+    <row r="1" spans="1:17" ht="24">
       <c r="A1" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75">
+      <c r="A2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="28"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="30" t="s">
-        <v>115</v>
-      </c>
       <c r="B2" s="30"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17" ht="15.75">
       <c r="A3" s="30"/>
       <c r="B3" s="30"/>
-    </row>
-    <row r="4" spans="1:16" ht="15.75">
+      <c r="O3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.75">
       <c r="A4" s="31" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="G4" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="H4" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="I4" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="J4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="K4" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="L4" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="M4" s="32" t="s">
         <v>124</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>125</v>
       </c>
       <c r="N4" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="15"/>
@@ -8317,8 +8838,12 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="15"/>
@@ -8332,8 +8857,12 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15"/>
@@ -8347,8 +8876,12 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="15"/>
@@ -8362,8 +8895,12 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15"/>
@@ -8377,8 +8914,12 @@
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="15"/>
@@ -8392,8 +8933,12 @@
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15"/>
@@ -8407,8 +8952,12 @@
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
@@ -8422,8 +8971,12 @@
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
@@ -8437,8 +8990,12 @@
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
@@ -8452,8 +9009,12 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
@@ -8467,8 +9028,12 @@
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
@@ -8482,8 +9047,12 @@
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
@@ -8497,8 +9066,12 @@
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
@@ -8512,8 +9085,12 @@
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
@@ -8527,8 +9104,12 @@
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
@@ -8542,8 +9123,12 @@
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
@@ -8557,15 +9142,22 @@
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="O3:Q3"/>
+  </mergeCells>
   <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>C5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F21">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>C5="library"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/datacontract/templates/excel/odcs-template.xlsx
+++ b/datacontract/templates/excel/odcs-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342FE4F4-9DE3-3540-BE91-7790BCC57F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB75899B-EBE7-F043-8A3F-9BE4C8EF552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$F$1000</definedName>
     <definedName name="constraints">Constraints!$A$4:$AZ$1000</definedName>
     <definedName name="context.instructions">Fundamentals!$C$25</definedName>
-    <definedName name="CustomProperties">'Custom Properties'!$A$5:$G$21</definedName>
+    <definedName name="CustomProperties">'Custom Properties'!$A$5:$H$21</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
     <definedName name="dataProduct">Fundamentals!$C$15</definedName>
     <definedName name="description.limitations">Fundamentals!$C$20</definedName>
@@ -69,7 +69,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AO$984</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AU$984</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -905,6 +905,30 @@
   <si>
     <t xml:space="preserve">This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Element Type</t>
+  </si>
+  <si>
+    <t>Distance Metric</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Embedding Model</t>
+  </si>
+  <si>
+    <t>Embedding Model Version</t>
+  </si>
+  <si>
+    <t>Value Type</t>
+  </si>
+  <si>
+    <t>Text</t>
   </si>
 </sst>
 </file>
@@ -14328,35 +14352,36 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29635FC6-19E5-6E43-84D3-3161FAC792B3}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="43.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="36.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="2"/>
+    <col min="5" max="5" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
@@ -14370,16 +14395,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
@@ -14389,159 +14417,213 @@
         <f>IF(owner &lt;&gt; "", owner, "")</f>
         <v/>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="D5:D61 E5:G21 B5:B22" xr:uid="{39D00745-E29F-BB4D-8EFF-9275524C1814}"/>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" sqref="B5:B22 F5:H21 D5:D61" xr:uid="{39D00745-E29F-BB4D-8EFF-9275524C1814}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A100" xr:uid="{9046F39E-9EB3-EF47-83AF-F83388AB159D}">
       <formula1>"Contract,Description,Server,Schema,Property,Enum Value,Synonym,Relationship,Quality,Support,Team,Team Member,Role,SLA,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E5:E100" xr:uid="{FD2B148B-B740-B14F-B337-F0CE13B025AB}">
+      <formula1>"Text,JSON"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15500,7 +15582,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -15521,28 +15603,28 @@
     <col min="18" max="22" width="19" style="2" customWidth="1"/>
     <col min="23" max="23" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="40" width="15.5" style="2" customWidth="1"/>
-    <col min="41" max="41" width="44.33203125" style="2" customWidth="1"/>
-    <col min="42" max="44" width="15.83203125" style="2" customWidth="1"/>
-    <col min="45" max="16384" width="8.83203125" style="2"/>
+    <col min="25" max="46" width="15.5" style="2" customWidth="1"/>
+    <col min="47" max="47" width="44.33203125" style="2" customWidth="1"/>
+    <col min="48" max="50" width="15.83203125" style="2" customWidth="1"/>
+    <col min="51" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -15553,7 +15635,7 @@
       <c r="D5" s="36"/>
       <c r="E5" s="36"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
@@ -15564,7 +15646,7 @@
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -15573,7 +15655,7 @@
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -15582,7 +15664,7 @@
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -15591,7 +15673,7 @@
       <c r="D9" s="38"/>
       <c r="E9" s="39"/>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
@@ -15600,7 +15682,7 @@
       <c r="D10" s="38"/>
       <c r="E10" s="39"/>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
@@ -15609,7 +15691,7 @@
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
@@ -15618,7 +15700,7 @@
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>242</v>
       </c>
@@ -15627,7 +15709,7 @@
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>218</v>
       </c>
@@ -15636,7 +15718,7 @@
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
       <c r="E15" s="2"/>
       <c r="Y15" s="19" t="s">
         <v>77</v>
@@ -15654,14 +15736,20 @@
       <c r="AJ15" s="20"/>
       <c r="AK15" s="20"/>
       <c r="AL15" s="20"/>
-      <c r="AM15" s="21"/>
-      <c r="AP15" s="19" t="s">
-        <v>31</v>
-      </c>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="20"/>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS15" s="21"/>
+      <c r="AV15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AW15" s="20"/>
+      <c r="AX15" s="20"/>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>0</v>
       </c>
@@ -15780,16 +15868,34 @@
         <v>87</v>
       </c>
       <c r="AN16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="AO16" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AP16" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AQ16" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR16" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS16" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="AT16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AO16" s="10" t="s">
+      <c r="AU16" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="10"/>
-      <c r="AR16" s="10"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AV16" s="10"/>
+      <c r="AW16" s="10"/>
+      <c r="AX16" s="10"/>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -15820,22 +15926,28 @@
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="15"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
       <c r="AI17" s="15"/>
       <c r="AJ17" s="15"/>
       <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
       <c r="AN17" s="15"/>
-      <c r="AO17" s="28"/>
+      <c r="AO17" s="15"/>
       <c r="AP17" s="15"/>
       <c r="AQ17" s="15"/>
       <c r="AR17" s="15"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS17" s="15"/>
+      <c r="AT17" s="15"/>
+      <c r="AU17" s="28"/>
+      <c r="AV17" s="15"/>
+      <c r="AW17" s="15"/>
+      <c r="AX17" s="15"/>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -15866,22 +15978,28 @@
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
       <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
       <c r="AI18" s="15"/>
       <c r="AJ18" s="15"/>
       <c r="AK18" s="15"/>
       <c r="AL18" s="15"/>
       <c r="AM18" s="15"/>
       <c r="AN18" s="15"/>
-      <c r="AO18" s="28"/>
+      <c r="AO18" s="15"/>
       <c r="AP18" s="15"/>
       <c r="AQ18" s="15"/>
       <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS18" s="15"/>
+      <c r="AT18" s="15"/>
+      <c r="AU18" s="28"/>
+      <c r="AV18" s="15"/>
+      <c r="AW18" s="15"/>
+      <c r="AX18" s="15"/>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -15912,22 +16030,28 @@
       <c r="AB19" s="15"/>
       <c r="AC19" s="15"/>
       <c r="AD19" s="15"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="15"/>
-      <c r="AG19" s="15"/>
-      <c r="AH19" s="15"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
       <c r="AI19" s="15"/>
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
       <c r="AN19" s="15"/>
-      <c r="AO19" s="28"/>
+      <c r="AO19" s="15"/>
       <c r="AP19" s="15"/>
       <c r="AQ19" s="15"/>
       <c r="AR19" s="15"/>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS19" s="15"/>
+      <c r="AT19" s="15"/>
+      <c r="AU19" s="28"/>
+      <c r="AV19" s="15"/>
+      <c r="AW19" s="15"/>
+      <c r="AX19" s="15"/>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -15958,22 +16082,28 @@
       <c r="AB20" s="15"/>
       <c r="AC20" s="15"/>
       <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="15"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
       <c r="AI20" s="15"/>
       <c r="AJ20" s="15"/>
       <c r="AK20" s="15"/>
       <c r="AL20" s="15"/>
       <c r="AM20" s="15"/>
       <c r="AN20" s="15"/>
-      <c r="AO20" s="28"/>
+      <c r="AO20" s="15"/>
       <c r="AP20" s="15"/>
       <c r="AQ20" s="15"/>
       <c r="AR20" s="15"/>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS20" s="15"/>
+      <c r="AT20" s="15"/>
+      <c r="AU20" s="28"/>
+      <c r="AV20" s="15"/>
+      <c r="AW20" s="15"/>
+      <c r="AX20" s="15"/>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -16004,22 +16134,28 @@
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
-      <c r="AE21" s="15"/>
-      <c r="AF21" s="15"/>
-      <c r="AG21" s="15"/>
-      <c r="AH21" s="15"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="16"/>
       <c r="AI21" s="15"/>
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>
       <c r="AN21" s="15"/>
-      <c r="AO21" s="28"/>
+      <c r="AO21" s="15"/>
       <c r="AP21" s="15"/>
       <c r="AQ21" s="15"/>
       <c r="AR21" s="15"/>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS21" s="15"/>
+      <c r="AT21" s="15"/>
+      <c r="AU21" s="28"/>
+      <c r="AV21" s="15"/>
+      <c r="AW21" s="15"/>
+      <c r="AX21" s="15"/>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -16050,22 +16186,28 @@
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
       <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="15"/>
-      <c r="AH22" s="15"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="16"/>
       <c r="AI22" s="15"/>
       <c r="AJ22" s="15"/>
       <c r="AK22" s="15"/>
       <c r="AL22" s="15"/>
       <c r="AM22" s="15"/>
       <c r="AN22" s="15"/>
-      <c r="AO22" s="28"/>
+      <c r="AO22" s="15"/>
       <c r="AP22" s="15"/>
       <c r="AQ22" s="15"/>
       <c r="AR22" s="15"/>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS22" s="15"/>
+      <c r="AT22" s="15"/>
+      <c r="AU22" s="28"/>
+      <c r="AV22" s="15"/>
+      <c r="AW22" s="15"/>
+      <c r="AX22" s="15"/>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A23" s="17"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -16096,22 +16238,28 @@
       <c r="AB23" s="15"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="15"/>
-      <c r="AH23" s="15"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="16"/>
       <c r="AI23" s="15"/>
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
       <c r="AL23" s="15"/>
       <c r="AM23" s="15"/>
       <c r="AN23" s="15"/>
-      <c r="AO23" s="28"/>
+      <c r="AO23" s="15"/>
       <c r="AP23" s="15"/>
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS23" s="15"/>
+      <c r="AT23" s="15"/>
+      <c r="AU23" s="28"/>
+      <c r="AV23" s="15"/>
+      <c r="AW23" s="15"/>
+      <c r="AX23" s="15"/>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -16142,22 +16290,28 @@
       <c r="AB24" s="15"/>
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
-      <c r="AE24" s="15"/>
-      <c r="AF24" s="15"/>
-      <c r="AG24" s="15"/>
-      <c r="AH24" s="15"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="16"/>
       <c r="AI24" s="15"/>
       <c r="AJ24" s="15"/>
       <c r="AK24" s="15"/>
       <c r="AL24" s="15"/>
       <c r="AM24" s="15"/>
       <c r="AN24" s="15"/>
-      <c r="AO24" s="28"/>
+      <c r="AO24" s="15"/>
       <c r="AP24" s="15"/>
       <c r="AQ24" s="15"/>
       <c r="AR24" s="15"/>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS24" s="15"/>
+      <c r="AT24" s="15"/>
+      <c r="AU24" s="28"/>
+      <c r="AV24" s="15"/>
+      <c r="AW24" s="15"/>
+      <c r="AX24" s="15"/>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -16188,22 +16342,28 @@
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
       <c r="AI25" s="15"/>
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
       <c r="AL25" s="15"/>
       <c r="AM25" s="15"/>
       <c r="AN25" s="15"/>
-      <c r="AO25" s="28"/>
+      <c r="AO25" s="15"/>
       <c r="AP25" s="15"/>
       <c r="AQ25" s="15"/>
       <c r="AR25" s="15"/>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS25" s="15"/>
+      <c r="AT25" s="15"/>
+      <c r="AU25" s="28"/>
+      <c r="AV25" s="15"/>
+      <c r="AW25" s="15"/>
+      <c r="AX25" s="15"/>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -16234,22 +16394,28 @@
       <c r="AB26" s="15"/>
       <c r="AC26" s="15"/>
       <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="16"/>
       <c r="AI26" s="15"/>
       <c r="AJ26" s="15"/>
       <c r="AK26" s="15"/>
       <c r="AL26" s="15"/>
       <c r="AM26" s="15"/>
       <c r="AN26" s="15"/>
-      <c r="AO26" s="28"/>
+      <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS26" s="15"/>
+      <c r="AT26" s="15"/>
+      <c r="AU26" s="28"/>
+      <c r="AV26" s="15"/>
+      <c r="AW26" s="15"/>
+      <c r="AX26" s="15"/>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -16280,22 +16446,28 @@
       <c r="AB27" s="15"/>
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
-      <c r="AH27" s="15"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="16"/>
       <c r="AI27" s="15"/>
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
       <c r="AL27" s="15"/>
       <c r="AM27" s="15"/>
       <c r="AN27" s="15"/>
-      <c r="AO27" s="28"/>
+      <c r="AO27" s="15"/>
       <c r="AP27" s="15"/>
       <c r="AQ27" s="15"/>
       <c r="AR27" s="15"/>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS27" s="15"/>
+      <c r="AT27" s="15"/>
+      <c r="AU27" s="28"/>
+      <c r="AV27" s="15"/>
+      <c r="AW27" s="15"/>
+      <c r="AX27" s="15"/>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -16326,22 +16498,28 @@
       <c r="AB28" s="15"/>
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
       <c r="AI28" s="15"/>
       <c r="AJ28" s="15"/>
       <c r="AK28" s="15"/>
       <c r="AL28" s="15"/>
       <c r="AM28" s="15"/>
       <c r="AN28" s="15"/>
-      <c r="AO28" s="28"/>
+      <c r="AO28" s="15"/>
       <c r="AP28" s="15"/>
       <c r="AQ28" s="15"/>
       <c r="AR28" s="15"/>
-    </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS28" s="15"/>
+      <c r="AT28" s="15"/>
+      <c r="AU28" s="28"/>
+      <c r="AV28" s="15"/>
+      <c r="AW28" s="15"/>
+      <c r="AX28" s="15"/>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -16372,22 +16550,28 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AH29" s="15"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
       <c r="AI29" s="15"/>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
       <c r="AL29" s="15"/>
       <c r="AM29" s="15"/>
       <c r="AN29" s="15"/>
-      <c r="AO29" s="28"/>
+      <c r="AO29" s="15"/>
       <c r="AP29" s="15"/>
       <c r="AQ29" s="15"/>
       <c r="AR29" s="15"/>
-    </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS29" s="15"/>
+      <c r="AT29" s="15"/>
+      <c r="AU29" s="28"/>
+      <c r="AV29" s="15"/>
+      <c r="AW29" s="15"/>
+      <c r="AX29" s="15"/>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -16418,22 +16602,28 @@
       <c r="AB30" s="15"/>
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="16"/>
       <c r="AI30" s="15"/>
       <c r="AJ30" s="15"/>
       <c r="AK30" s="15"/>
       <c r="AL30" s="15"/>
       <c r="AM30" s="15"/>
       <c r="AN30" s="15"/>
-      <c r="AO30" s="28"/>
+      <c r="AO30" s="15"/>
       <c r="AP30" s="15"/>
       <c r="AQ30" s="15"/>
       <c r="AR30" s="15"/>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS30" s="15"/>
+      <c r="AT30" s="15"/>
+      <c r="AU30" s="28"/>
+      <c r="AV30" s="15"/>
+      <c r="AW30" s="15"/>
+      <c r="AX30" s="15"/>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -16464,22 +16654,28 @@
       <c r="AB31" s="15"/>
       <c r="AC31" s="15"/>
       <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="15"/>
-      <c r="AG31" s="15"/>
-      <c r="AH31" s="15"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="16"/>
       <c r="AI31" s="15"/>
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
       <c r="AL31" s="15"/>
       <c r="AM31" s="15"/>
       <c r="AN31" s="15"/>
-      <c r="AO31" s="28"/>
+      <c r="AO31" s="15"/>
       <c r="AP31" s="15"/>
       <c r="AQ31" s="15"/>
       <c r="AR31" s="15"/>
-    </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS31" s="15"/>
+      <c r="AT31" s="15"/>
+      <c r="AU31" s="28"/>
+      <c r="AV31" s="15"/>
+      <c r="AW31" s="15"/>
+      <c r="AX31" s="15"/>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -16510,22 +16706,28 @@
       <c r="AB32" s="15"/>
       <c r="AC32" s="15"/>
       <c r="AD32" s="15"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="15"/>
-      <c r="AG32" s="15"/>
-      <c r="AH32" s="15"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="16"/>
       <c r="AI32" s="15"/>
       <c r="AJ32" s="15"/>
       <c r="AK32" s="15"/>
       <c r="AL32" s="15"/>
       <c r="AM32" s="15"/>
       <c r="AN32" s="15"/>
-      <c r="AO32" s="28"/>
+      <c r="AO32" s="15"/>
       <c r="AP32" s="15"/>
       <c r="AQ32" s="15"/>
       <c r="AR32" s="15"/>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS32" s="15"/>
+      <c r="AT32" s="15"/>
+      <c r="AU32" s="28"/>
+      <c r="AV32" s="15"/>
+      <c r="AW32" s="15"/>
+      <c r="AX32" s="15"/>
+    </row>
+    <row r="33" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -16556,22 +16758,28 @@
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
       <c r="AD33" s="15"/>
-      <c r="AE33" s="15"/>
-      <c r="AF33" s="15"/>
-      <c r="AG33" s="15"/>
-      <c r="AH33" s="15"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="16"/>
       <c r="AI33" s="15"/>
       <c r="AJ33" s="15"/>
       <c r="AK33" s="15"/>
       <c r="AL33" s="15"/>
       <c r="AM33" s="15"/>
       <c r="AN33" s="15"/>
-      <c r="AO33" s="28"/>
+      <c r="AO33" s="15"/>
       <c r="AP33" s="15"/>
       <c r="AQ33" s="15"/>
       <c r="AR33" s="15"/>
-    </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS33" s="15"/>
+      <c r="AT33" s="15"/>
+      <c r="AU33" s="28"/>
+      <c r="AV33" s="15"/>
+      <c r="AW33" s="15"/>
+      <c r="AX33" s="15"/>
+    </row>
+    <row r="34" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -16602,22 +16810,28 @@
       <c r="AB34" s="15"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="15"/>
-      <c r="AE34" s="15"/>
-      <c r="AF34" s="15"/>
-      <c r="AG34" s="15"/>
-      <c r="AH34" s="15"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="16"/>
       <c r="AI34" s="15"/>
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
       <c r="AL34" s="15"/>
       <c r="AM34" s="15"/>
       <c r="AN34" s="15"/>
-      <c r="AO34" s="28"/>
+      <c r="AO34" s="15"/>
       <c r="AP34" s="15"/>
       <c r="AQ34" s="15"/>
       <c r="AR34" s="15"/>
-    </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS34" s="15"/>
+      <c r="AT34" s="15"/>
+      <c r="AU34" s="28"/>
+      <c r="AV34" s="15"/>
+      <c r="AW34" s="15"/>
+      <c r="AX34" s="15"/>
+    </row>
+    <row r="35" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -16648,22 +16862,28 @@
       <c r="AB35" s="15"/>
       <c r="AC35" s="15"/>
       <c r="AD35" s="15"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="15"/>
-      <c r="AG35" s="15"/>
-      <c r="AH35" s="15"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
       <c r="AI35" s="15"/>
       <c r="AJ35" s="15"/>
       <c r="AK35" s="15"/>
       <c r="AL35" s="15"/>
       <c r="AM35" s="15"/>
       <c r="AN35" s="15"/>
-      <c r="AO35" s="28"/>
+      <c r="AO35" s="15"/>
       <c r="AP35" s="15"/>
       <c r="AQ35" s="15"/>
       <c r="AR35" s="15"/>
-    </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS35" s="15"/>
+      <c r="AT35" s="15"/>
+      <c r="AU35" s="28"/>
+      <c r="AV35" s="15"/>
+      <c r="AW35" s="15"/>
+      <c r="AX35" s="15"/>
+    </row>
+    <row r="36" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -16694,22 +16914,28 @@
       <c r="AB36" s="15"/>
       <c r="AC36" s="15"/>
       <c r="AD36" s="15"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="15"/>
-      <c r="AG36" s="15"/>
-      <c r="AH36" s="15"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="16"/>
       <c r="AI36" s="15"/>
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
       <c r="AL36" s="15"/>
       <c r="AM36" s="15"/>
       <c r="AN36" s="15"/>
-      <c r="AO36" s="28"/>
+      <c r="AO36" s="15"/>
       <c r="AP36" s="15"/>
       <c r="AQ36" s="15"/>
       <c r="AR36" s="15"/>
-    </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS36" s="15"/>
+      <c r="AT36" s="15"/>
+      <c r="AU36" s="28"/>
+      <c r="AV36" s="15"/>
+      <c r="AW36" s="15"/>
+      <c r="AX36" s="15"/>
+    </row>
+    <row r="37" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -16740,22 +16966,28 @@
       <c r="AB37" s="15"/>
       <c r="AC37" s="15"/>
       <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="15"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
       <c r="AI37" s="15"/>
       <c r="AJ37" s="15"/>
       <c r="AK37" s="15"/>
       <c r="AL37" s="15"/>
       <c r="AM37" s="15"/>
       <c r="AN37" s="15"/>
-      <c r="AO37" s="28"/>
+      <c r="AO37" s="15"/>
       <c r="AP37" s="15"/>
       <c r="AQ37" s="15"/>
       <c r="AR37" s="15"/>
-    </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS37" s="15"/>
+      <c r="AT37" s="15"/>
+      <c r="AU37" s="28"/>
+      <c r="AV37" s="15"/>
+      <c r="AW37" s="15"/>
+      <c r="AX37" s="15"/>
+    </row>
+    <row r="38" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -16786,22 +17018,28 @@
       <c r="AB38" s="15"/>
       <c r="AC38" s="15"/>
       <c r="AD38" s="15"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="15"/>
-      <c r="AG38" s="15"/>
-      <c r="AH38" s="15"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="16"/>
       <c r="AI38" s="15"/>
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
       <c r="AL38" s="15"/>
       <c r="AM38" s="15"/>
       <c r="AN38" s="15"/>
-      <c r="AO38" s="28"/>
+      <c r="AO38" s="15"/>
       <c r="AP38" s="15"/>
       <c r="AQ38" s="15"/>
       <c r="AR38" s="15"/>
-    </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS38" s="15"/>
+      <c r="AT38" s="15"/>
+      <c r="AU38" s="28"/>
+      <c r="AV38" s="15"/>
+      <c r="AW38" s="15"/>
+      <c r="AX38" s="15"/>
+    </row>
+    <row r="39" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -16832,22 +17070,28 @@
       <c r="AB39" s="15"/>
       <c r="AC39" s="15"/>
       <c r="AD39" s="15"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
-      <c r="AH39" s="15"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="16"/>
       <c r="AI39" s="15"/>
       <c r="AJ39" s="15"/>
       <c r="AK39" s="15"/>
       <c r="AL39" s="15"/>
       <c r="AM39" s="15"/>
       <c r="AN39" s="15"/>
-      <c r="AO39" s="28"/>
+      <c r="AO39" s="15"/>
       <c r="AP39" s="15"/>
       <c r="AQ39" s="15"/>
       <c r="AR39" s="15"/>
-    </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS39" s="15"/>
+      <c r="AT39" s="15"/>
+      <c r="AU39" s="28"/>
+      <c r="AV39" s="15"/>
+      <c r="AW39" s="15"/>
+      <c r="AX39" s="15"/>
+    </row>
+    <row r="40" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -16878,22 +17122,28 @@
       <c r="AB40" s="15"/>
       <c r="AC40" s="15"/>
       <c r="AD40" s="15"/>
-      <c r="AE40" s="15"/>
-      <c r="AF40" s="15"/>
-      <c r="AG40" s="15"/>
-      <c r="AH40" s="15"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="16"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="16"/>
       <c r="AI40" s="15"/>
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
       <c r="AL40" s="15"/>
       <c r="AM40" s="15"/>
       <c r="AN40" s="15"/>
-      <c r="AO40" s="28"/>
+      <c r="AO40" s="15"/>
       <c r="AP40" s="15"/>
       <c r="AQ40" s="15"/>
       <c r="AR40" s="15"/>
-    </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS40" s="15"/>
+      <c r="AT40" s="15"/>
+      <c r="AU40" s="28"/>
+      <c r="AV40" s="15"/>
+      <c r="AW40" s="15"/>
+      <c r="AX40" s="15"/>
+    </row>
+    <row r="41" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -16924,22 +17174,28 @@
       <c r="AB41" s="15"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="15"/>
-      <c r="AE41" s="15"/>
-      <c r="AF41" s="15"/>
-      <c r="AG41" s="15"/>
-      <c r="AH41" s="15"/>
+      <c r="AE41" s="16"/>
+      <c r="AF41" s="16"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="16"/>
       <c r="AI41" s="15"/>
       <c r="AJ41" s="15"/>
       <c r="AK41" s="15"/>
       <c r="AL41" s="15"/>
       <c r="AM41" s="15"/>
       <c r="AN41" s="15"/>
-      <c r="AO41" s="28"/>
+      <c r="AO41" s="15"/>
       <c r="AP41" s="15"/>
       <c r="AQ41" s="15"/>
       <c r="AR41" s="15"/>
-    </row>
-    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS41" s="15"/>
+      <c r="AT41" s="15"/>
+      <c r="AU41" s="28"/>
+      <c r="AV41" s="15"/>
+      <c r="AW41" s="15"/>
+      <c r="AX41" s="15"/>
+    </row>
+    <row r="42" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -16970,22 +17226,28 @@
       <c r="AB42" s="15"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="15"/>
-      <c r="AE42" s="15"/>
-      <c r="AF42" s="15"/>
-      <c r="AG42" s="15"/>
-      <c r="AH42" s="15"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
       <c r="AI42" s="15"/>
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="15"/>
       <c r="AM42" s="15"/>
       <c r="AN42" s="15"/>
-      <c r="AO42" s="28"/>
+      <c r="AO42" s="15"/>
       <c r="AP42" s="15"/>
       <c r="AQ42" s="15"/>
       <c r="AR42" s="15"/>
-    </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS42" s="15"/>
+      <c r="AT42" s="15"/>
+      <c r="AU42" s="28"/>
+      <c r="AV42" s="15"/>
+      <c r="AW42" s="15"/>
+      <c r="AX42" s="15"/>
+    </row>
+    <row r="43" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -17016,22 +17278,28 @@
       <c r="AB43" s="15"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="15"/>
-      <c r="AE43" s="15"/>
-      <c r="AF43" s="15"/>
-      <c r="AG43" s="15"/>
-      <c r="AH43" s="15"/>
+      <c r="AE43" s="16"/>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="16"/>
       <c r="AI43" s="15"/>
       <c r="AJ43" s="15"/>
       <c r="AK43" s="15"/>
       <c r="AL43" s="15"/>
       <c r="AM43" s="15"/>
       <c r="AN43" s="15"/>
-      <c r="AO43" s="28"/>
+      <c r="AO43" s="15"/>
       <c r="AP43" s="15"/>
       <c r="AQ43" s="15"/>
       <c r="AR43" s="15"/>
-    </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS43" s="15"/>
+      <c r="AT43" s="15"/>
+      <c r="AU43" s="28"/>
+      <c r="AV43" s="15"/>
+      <c r="AW43" s="15"/>
+      <c r="AX43" s="15"/>
+    </row>
+    <row r="44" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -17062,22 +17330,28 @@
       <c r="AB44" s="15"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="15"/>
-      <c r="AE44" s="15"/>
-      <c r="AF44" s="15"/>
-      <c r="AG44" s="15"/>
-      <c r="AH44" s="15"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="16"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="16"/>
       <c r="AI44" s="15"/>
       <c r="AJ44" s="15"/>
       <c r="AK44" s="15"/>
       <c r="AL44" s="15"/>
       <c r="AM44" s="15"/>
       <c r="AN44" s="15"/>
-      <c r="AO44" s="28"/>
+      <c r="AO44" s="15"/>
       <c r="AP44" s="15"/>
       <c r="AQ44" s="15"/>
       <c r="AR44" s="15"/>
-    </row>
-    <row r="45" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS44" s="15"/>
+      <c r="AT44" s="15"/>
+      <c r="AU44" s="28"/>
+      <c r="AV44" s="15"/>
+      <c r="AW44" s="15"/>
+      <c r="AX44" s="15"/>
+    </row>
+    <row r="45" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17108,22 +17382,28 @@
       <c r="AB45" s="15"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="15"/>
-      <c r="AE45" s="15"/>
-      <c r="AF45" s="15"/>
-      <c r="AG45" s="15"/>
-      <c r="AH45" s="15"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="16"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="16"/>
       <c r="AI45" s="15"/>
       <c r="AJ45" s="15"/>
       <c r="AK45" s="15"/>
       <c r="AL45" s="15"/>
       <c r="AM45" s="15"/>
       <c r="AN45" s="15"/>
-      <c r="AO45" s="28"/>
+      <c r="AO45" s="15"/>
       <c r="AP45" s="15"/>
       <c r="AQ45" s="15"/>
       <c r="AR45" s="15"/>
-    </row>
-    <row r="46" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS45" s="15"/>
+      <c r="AT45" s="15"/>
+      <c r="AU45" s="28"/>
+      <c r="AV45" s="15"/>
+      <c r="AW45" s="15"/>
+      <c r="AX45" s="15"/>
+    </row>
+    <row r="46" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -17154,22 +17434,28 @@
       <c r="AB46" s="15"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="15"/>
-      <c r="AE46" s="15"/>
-      <c r="AF46" s="15"/>
-      <c r="AG46" s="15"/>
-      <c r="AH46" s="15"/>
+      <c r="AE46" s="16"/>
+      <c r="AF46" s="16"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="16"/>
       <c r="AI46" s="15"/>
       <c r="AJ46" s="15"/>
       <c r="AK46" s="15"/>
       <c r="AL46" s="15"/>
       <c r="AM46" s="15"/>
       <c r="AN46" s="15"/>
-      <c r="AO46" s="28"/>
+      <c r="AO46" s="15"/>
       <c r="AP46" s="15"/>
       <c r="AQ46" s="15"/>
       <c r="AR46" s="15"/>
-    </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS46" s="15"/>
+      <c r="AT46" s="15"/>
+      <c r="AU46" s="28"/>
+      <c r="AV46" s="15"/>
+      <c r="AW46" s="15"/>
+      <c r="AX46" s="15"/>
+    </row>
+    <row r="47" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -17200,22 +17486,28 @@
       <c r="AB47" s="15"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="15"/>
-      <c r="AE47" s="15"/>
-      <c r="AF47" s="15"/>
-      <c r="AG47" s="15"/>
-      <c r="AH47" s="15"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="16"/>
       <c r="AI47" s="15"/>
       <c r="AJ47" s="15"/>
       <c r="AK47" s="15"/>
       <c r="AL47" s="15"/>
       <c r="AM47" s="15"/>
       <c r="AN47" s="15"/>
-      <c r="AO47" s="28"/>
+      <c r="AO47" s="15"/>
       <c r="AP47" s="15"/>
       <c r="AQ47" s="15"/>
       <c r="AR47" s="15"/>
-    </row>
-    <row r="48" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS47" s="15"/>
+      <c r="AT47" s="15"/>
+      <c r="AU47" s="28"/>
+      <c r="AV47" s="15"/>
+      <c r="AW47" s="15"/>
+      <c r="AX47" s="15"/>
+    </row>
+    <row r="48" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -17246,22 +17538,28 @@
       <c r="AB48" s="15"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="15"/>
-      <c r="AE48" s="15"/>
-      <c r="AF48" s="15"/>
-      <c r="AG48" s="15"/>
-      <c r="AH48" s="15"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="16"/>
       <c r="AI48" s="15"/>
       <c r="AJ48" s="15"/>
       <c r="AK48" s="15"/>
       <c r="AL48" s="15"/>
       <c r="AM48" s="15"/>
       <c r="AN48" s="15"/>
-      <c r="AO48" s="28"/>
+      <c r="AO48" s="15"/>
       <c r="AP48" s="15"/>
       <c r="AQ48" s="15"/>
       <c r="AR48" s="15"/>
-    </row>
-    <row r="49" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS48" s="15"/>
+      <c r="AT48" s="15"/>
+      <c r="AU48" s="28"/>
+      <c r="AV48" s="15"/>
+      <c r="AW48" s="15"/>
+      <c r="AX48" s="15"/>
+    </row>
+    <row r="49" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17292,22 +17590,28 @@
       <c r="AB49" s="15"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="15"/>
-      <c r="AE49" s="15"/>
-      <c r="AF49" s="15"/>
-      <c r="AG49" s="15"/>
-      <c r="AH49" s="15"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="16"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="16"/>
       <c r="AI49" s="15"/>
       <c r="AJ49" s="15"/>
       <c r="AK49" s="15"/>
       <c r="AL49" s="15"/>
       <c r="AM49" s="15"/>
       <c r="AN49" s="15"/>
-      <c r="AO49" s="28"/>
+      <c r="AO49" s="15"/>
       <c r="AP49" s="15"/>
       <c r="AQ49" s="15"/>
       <c r="AR49" s="15"/>
-    </row>
-    <row r="50" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS49" s="15"/>
+      <c r="AT49" s="15"/>
+      <c r="AU49" s="28"/>
+      <c r="AV49" s="15"/>
+      <c r="AW49" s="15"/>
+      <c r="AX49" s="15"/>
+    </row>
+    <row r="50" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A50" s="17"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -17338,22 +17642,28 @@
       <c r="AB50" s="15"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="15"/>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="15"/>
-      <c r="AG50" s="15"/>
-      <c r="AH50" s="15"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="16"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="16"/>
       <c r="AI50" s="15"/>
       <c r="AJ50" s="15"/>
       <c r="AK50" s="15"/>
       <c r="AL50" s="15"/>
       <c r="AM50" s="15"/>
       <c r="AN50" s="15"/>
-      <c r="AO50" s="28"/>
+      <c r="AO50" s="15"/>
       <c r="AP50" s="15"/>
       <c r="AQ50" s="15"/>
       <c r="AR50" s="15"/>
-    </row>
-    <row r="51" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS50" s="15"/>
+      <c r="AT50" s="15"/>
+      <c r="AU50" s="28"/>
+      <c r="AV50" s="15"/>
+      <c r="AW50" s="15"/>
+      <c r="AX50" s="15"/>
+    </row>
+    <row r="51" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -17384,22 +17694,28 @@
       <c r="AB51" s="15"/>
       <c r="AC51" s="15"/>
       <c r="AD51" s="15"/>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="15"/>
-      <c r="AG51" s="15"/>
-      <c r="AH51" s="15"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="16"/>
       <c r="AI51" s="15"/>
       <c r="AJ51" s="15"/>
       <c r="AK51" s="15"/>
       <c r="AL51" s="15"/>
       <c r="AM51" s="15"/>
       <c r="AN51" s="15"/>
-      <c r="AO51" s="28"/>
+      <c r="AO51" s="15"/>
       <c r="AP51" s="15"/>
       <c r="AQ51" s="15"/>
       <c r="AR51" s="15"/>
-    </row>
-    <row r="52" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS51" s="15"/>
+      <c r="AT51" s="15"/>
+      <c r="AU51" s="28"/>
+      <c r="AV51" s="15"/>
+      <c r="AW51" s="15"/>
+      <c r="AX51" s="15"/>
+    </row>
+    <row r="52" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A52" s="17"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -17430,20 +17746,26 @@
       <c r="AB52" s="15"/>
       <c r="AC52" s="15"/>
       <c r="AD52" s="15"/>
-      <c r="AE52" s="15"/>
-      <c r="AF52" s="15"/>
-      <c r="AG52" s="15"/>
-      <c r="AH52" s="15"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="16"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="16"/>
       <c r="AI52" s="15"/>
       <c r="AJ52" s="15"/>
       <c r="AK52" s="15"/>
       <c r="AL52" s="15"/>
       <c r="AM52" s="15"/>
       <c r="AN52" s="15"/>
-      <c r="AO52" s="28"/>
+      <c r="AO52" s="15"/>
       <c r="AP52" s="15"/>
       <c r="AQ52" s="15"/>
       <c r="AR52" s="15"/>
+      <c r="AS52" s="15"/>
+      <c r="AT52" s="15"/>
+      <c r="AU52" s="28"/>
+      <c r="AV52" s="15"/>
+      <c r="AW52" s="15"/>
+      <c r="AX52" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -17458,14 +17780,14 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="17">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H17:H52" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 Y17:AR52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 AR17:AX52 Y17:AM52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -17481,15 +17803,24 @@
     <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AO16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AU16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
     <dataValidation type="list" allowBlank="1" sqref="K17:K103" xr:uid="{FC6EF137-EF73-574C-95CF-B57336C59E8E}">
       <formula1>"column,measure,dimension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L17:L103" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
+    <dataValidation type="list" allowBlank="1" sqref="L17:L103 AQ17:AQ100" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:E14" xr:uid="{D05E7DD6-9150-B941-B705-FF6CFA22D7F9}">
       <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="AO17:AO100" xr:uid="{95DD2EA0-6986-414F-8048-0D9B55450EB2}">
+      <formula1>"bfloat16,binary,float16,float32,float64,int8,uint8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="AP17:AP100" xr:uid="{EF98B3E8-396D-0F48-A972-E0956219870A}">
+      <formula1>"cosine,dotProduct,euclidean,hamming,manhattan"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" sqref="AN17:AN100" xr:uid="{F44F2772-48BF-B94D-9469-EC67E27A68CF}">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datacontract/templates/excel/odcs-template.xlsx
+++ b/datacontract/templates/excel/odcs-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB75899B-EBE7-F043-8A3F-9BE4C8EF552B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3875D753-AACC-B04A-B375-AAA28B30B143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -39,20 +39,21 @@
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
     <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$F$1000</definedName>
     <definedName name="constraints">Constraints!$A$4:$AZ$1000</definedName>
-    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
+    <definedName name="context.instructions">Fundamentals!$C$26</definedName>
+    <definedName name="contractCreatedTs">Fundamentals!$C$11</definedName>
     <definedName name="CustomProperties">'Custom Properties'!$A$5:$H$21</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
-    <definedName name="dataProduct">Fundamentals!$C$15</definedName>
-    <definedName name="description.limitations">Fundamentals!$C$20</definedName>
-    <definedName name="description.purpose">Fundamentals!$C$19</definedName>
-    <definedName name="description.usage">Fundamentals!$C$21</definedName>
-    <definedName name="domain">Fundamentals!$C$14</definedName>
+    <definedName name="dataProduct">Fundamentals!$C$16</definedName>
+    <definedName name="description.limitations">Fundamentals!$C$21</definedName>
+    <definedName name="description.purpose">Fundamentals!$C$20</definedName>
+    <definedName name="description.usage">Fundamentals!$C$22</definedName>
+    <definedName name="domain">Fundamentals!$C$15</definedName>
     <definedName name="enum">Enums!$A$4:$AZ$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
     <definedName name="name">Fundamentals!$C$8</definedName>
-    <definedName name="owner">Fundamentals!$C$12</definedName>
+    <definedName name="owner">Fundamentals!$C$13</definedName>
     <definedName name="price.id">Pricing!$B$7</definedName>
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
@@ -69,7 +70,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AU$984</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AW$984</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
@@ -104,13 +105,13 @@
     <definedName name="status">Fundamentals!$C$10</definedName>
     <definedName name="support">Support!$A$4:$AZ$1000</definedName>
     <definedName name="synonyms">Synonyms!$A$4:$AZ$1000</definedName>
-    <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="team">Team!$A$10:$AZ$1006</definedName>
+    <definedName name="tags">Fundamentals!$C$24</definedName>
+    <definedName name="team">Team!$A$10:$BA$1006</definedName>
     <definedName name="team.description">Team!$B$5</definedName>
     <definedName name="team.id">Team!$B$7</definedName>
     <definedName name="team.name">Team!$B$4</definedName>
     <definedName name="team.tags">Team!$B$6</definedName>
-    <definedName name="tenant">Fundamentals!$C$16</definedName>
+    <definedName name="tenant">Fundamentals!$C$17</definedName>
     <definedName name="verifiedStatements">'Verified Statements'!$A$4:$AZ$1000</definedName>
     <definedName name="version">Fundamentals!$C$9</definedName>
   </definedNames>
@@ -132,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="260">
   <si>
     <t>Property</t>
   </si>
@@ -929,6 +930,15 @@
   </si>
   <si>
     <t>Text</t>
+  </si>
+  <si>
+    <t>Contract Created</t>
+  </si>
+  <si>
+    <t>Timezone</t>
+  </si>
+  <si>
+    <t>Default Timezone</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1232,6 +1242,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -15392,7 +15405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ABE851-FB8B-2145-B7F8-5CF6722D55A6}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="2" customWidth="1"/>
@@ -15470,32 +15483,31 @@
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="34"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="5"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="5"/>
-      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="5"/>
@@ -15503,77 +15515,85 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="5"/>
+      <c r="B19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
         <v>241</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="G11:L13 G17:L24" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
+    <dataValidation type="list" allowBlank="1" sqref="G12:L14 G18:L25" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D22 D17:D18 D11:D13 D24" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
+    <dataValidation type="list" allowBlank="1" sqref="D23 D18:D19 D12:D14 D25" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
       <formula1>"string,number,integer,boolean,array,object"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C12" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
-    <dataValidation allowBlank="1" sqref="C11:C13 C17:C18 C22:C65" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C13" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
+    <dataValidation allowBlank="1" sqref="C12:C14 C18:C19 C23:C66" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15582,7 +15602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -15603,122 +15623,122 @@
     <col min="18" max="22" width="19" style="2" customWidth="1"/>
     <col min="23" max="23" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="46" width="15.5" style="2" customWidth="1"/>
-    <col min="47" max="47" width="44.33203125" style="2" customWidth="1"/>
-    <col min="48" max="50" width="15.83203125" style="2" customWidth="1"/>
-    <col min="51" max="16384" width="8.83203125" style="2"/>
+    <col min="25" max="48" width="15.5" style="2" customWidth="1"/>
+    <col min="49" max="49" width="44.33203125" style="2" customWidth="1"/>
+    <col min="50" max="52" width="15.83203125" style="2" customWidth="1"/>
+    <col min="53" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-    </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-    </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-    </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40"/>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-    </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-    </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
       <c r="E15" s="2"/>
       <c r="Y15" s="19" t="s">
         <v>77</v>
@@ -15742,14 +15762,16 @@
       <c r="AP15" s="20"/>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20"/>
-      <c r="AS15" s="21"/>
-      <c r="AV15" s="19" t="s">
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="20"/>
+      <c r="AU15" s="21"/>
+      <c r="AX15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AW15" s="20"/>
-      <c r="AX15" s="20"/>
-    </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY15" s="20"/>
+      <c r="AZ15" s="20"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>0</v>
       </c>
@@ -15886,16 +15908,22 @@
         <v>254</v>
       </c>
       <c r="AT16" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AU16" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AV16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AU16" s="10" t="s">
+      <c r="AW16" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AV16" s="10"/>
-      <c r="AW16" s="10"/>
       <c r="AX16" s="10"/>
-    </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY16" s="10"/>
+      <c r="AZ16" s="10"/>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -15942,12 +15970,14 @@
       <c r="AR17" s="15"/>
       <c r="AS17" s="15"/>
       <c r="AT17" s="15"/>
-      <c r="AU17" s="28"/>
+      <c r="AU17" s="15"/>
       <c r="AV17" s="15"/>
-      <c r="AW17" s="15"/>
+      <c r="AW17" s="28"/>
       <c r="AX17" s="15"/>
-    </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY17" s="15"/>
+      <c r="AZ17" s="15"/>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -15994,12 +16024,14 @@
       <c r="AR18" s="15"/>
       <c r="AS18" s="15"/>
       <c r="AT18" s="15"/>
-      <c r="AU18" s="28"/>
+      <c r="AU18" s="15"/>
       <c r="AV18" s="15"/>
-      <c r="AW18" s="15"/>
+      <c r="AW18" s="28"/>
       <c r="AX18" s="15"/>
-    </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY18" s="15"/>
+      <c r="AZ18" s="15"/>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -16046,12 +16078,14 @@
       <c r="AR19" s="15"/>
       <c r="AS19" s="15"/>
       <c r="AT19" s="15"/>
-      <c r="AU19" s="28"/>
+      <c r="AU19" s="15"/>
       <c r="AV19" s="15"/>
-      <c r="AW19" s="15"/>
+      <c r="AW19" s="28"/>
       <c r="AX19" s="15"/>
-    </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY19" s="15"/>
+      <c r="AZ19" s="15"/>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -16098,12 +16132,14 @@
       <c r="AR20" s="15"/>
       <c r="AS20" s="15"/>
       <c r="AT20" s="15"/>
-      <c r="AU20" s="28"/>
+      <c r="AU20" s="15"/>
       <c r="AV20" s="15"/>
-      <c r="AW20" s="15"/>
+      <c r="AW20" s="28"/>
       <c r="AX20" s="15"/>
-    </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY20" s="15"/>
+      <c r="AZ20" s="15"/>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -16150,12 +16186,14 @@
       <c r="AR21" s="15"/>
       <c r="AS21" s="15"/>
       <c r="AT21" s="15"/>
-      <c r="AU21" s="28"/>
+      <c r="AU21" s="15"/>
       <c r="AV21" s="15"/>
-      <c r="AW21" s="15"/>
+      <c r="AW21" s="28"/>
       <c r="AX21" s="15"/>
-    </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY21" s="15"/>
+      <c r="AZ21" s="15"/>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -16202,12 +16240,14 @@
       <c r="AR22" s="15"/>
       <c r="AS22" s="15"/>
       <c r="AT22" s="15"/>
-      <c r="AU22" s="28"/>
+      <c r="AU22" s="15"/>
       <c r="AV22" s="15"/>
-      <c r="AW22" s="15"/>
+      <c r="AW22" s="28"/>
       <c r="AX22" s="15"/>
-    </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY22" s="15"/>
+      <c r="AZ22" s="15"/>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A23" s="17"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -16254,12 +16294,14 @@
       <c r="AR23" s="15"/>
       <c r="AS23" s="15"/>
       <c r="AT23" s="15"/>
-      <c r="AU23" s="28"/>
+      <c r="AU23" s="15"/>
       <c r="AV23" s="15"/>
-      <c r="AW23" s="15"/>
+      <c r="AW23" s="28"/>
       <c r="AX23" s="15"/>
-    </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY23" s="15"/>
+      <c r="AZ23" s="15"/>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -16306,12 +16348,14 @@
       <c r="AR24" s="15"/>
       <c r="AS24" s="15"/>
       <c r="AT24" s="15"/>
-      <c r="AU24" s="28"/>
+      <c r="AU24" s="15"/>
       <c r="AV24" s="15"/>
-      <c r="AW24" s="15"/>
+      <c r="AW24" s="28"/>
       <c r="AX24" s="15"/>
-    </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY24" s="15"/>
+      <c r="AZ24" s="15"/>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -16358,12 +16402,14 @@
       <c r="AR25" s="15"/>
       <c r="AS25" s="15"/>
       <c r="AT25" s="15"/>
-      <c r="AU25" s="28"/>
+      <c r="AU25" s="15"/>
       <c r="AV25" s="15"/>
-      <c r="AW25" s="15"/>
+      <c r="AW25" s="28"/>
       <c r="AX25" s="15"/>
-    </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY25" s="15"/>
+      <c r="AZ25" s="15"/>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -16410,12 +16456,14 @@
       <c r="AR26" s="15"/>
       <c r="AS26" s="15"/>
       <c r="AT26" s="15"/>
-      <c r="AU26" s="28"/>
+      <c r="AU26" s="15"/>
       <c r="AV26" s="15"/>
-      <c r="AW26" s="15"/>
+      <c r="AW26" s="28"/>
       <c r="AX26" s="15"/>
-    </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY26" s="15"/>
+      <c r="AZ26" s="15"/>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -16462,12 +16510,14 @@
       <c r="AR27" s="15"/>
       <c r="AS27" s="15"/>
       <c r="AT27" s="15"/>
-      <c r="AU27" s="28"/>
+      <c r="AU27" s="15"/>
       <c r="AV27" s="15"/>
-      <c r="AW27" s="15"/>
+      <c r="AW27" s="28"/>
       <c r="AX27" s="15"/>
-    </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY27" s="15"/>
+      <c r="AZ27" s="15"/>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -16514,12 +16564,14 @@
       <c r="AR28" s="15"/>
       <c r="AS28" s="15"/>
       <c r="AT28" s="15"/>
-      <c r="AU28" s="28"/>
+      <c r="AU28" s="15"/>
       <c r="AV28" s="15"/>
-      <c r="AW28" s="15"/>
+      <c r="AW28" s="28"/>
       <c r="AX28" s="15"/>
-    </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY28" s="15"/>
+      <c r="AZ28" s="15"/>
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -16566,12 +16618,14 @@
       <c r="AR29" s="15"/>
       <c r="AS29" s="15"/>
       <c r="AT29" s="15"/>
-      <c r="AU29" s="28"/>
+      <c r="AU29" s="15"/>
       <c r="AV29" s="15"/>
-      <c r="AW29" s="15"/>
+      <c r="AW29" s="28"/>
       <c r="AX29" s="15"/>
-    </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY29" s="15"/>
+      <c r="AZ29" s="15"/>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -16618,12 +16672,14 @@
       <c r="AR30" s="15"/>
       <c r="AS30" s="15"/>
       <c r="AT30" s="15"/>
-      <c r="AU30" s="28"/>
+      <c r="AU30" s="15"/>
       <c r="AV30" s="15"/>
-      <c r="AW30" s="15"/>
+      <c r="AW30" s="28"/>
       <c r="AX30" s="15"/>
-    </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY30" s="15"/>
+      <c r="AZ30" s="15"/>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -16670,12 +16726,14 @@
       <c r="AR31" s="15"/>
       <c r="AS31" s="15"/>
       <c r="AT31" s="15"/>
-      <c r="AU31" s="28"/>
+      <c r="AU31" s="15"/>
       <c r="AV31" s="15"/>
-      <c r="AW31" s="15"/>
+      <c r="AW31" s="28"/>
       <c r="AX31" s="15"/>
-    </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY31" s="15"/>
+      <c r="AZ31" s="15"/>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -16722,12 +16780,14 @@
       <c r="AR32" s="15"/>
       <c r="AS32" s="15"/>
       <c r="AT32" s="15"/>
-      <c r="AU32" s="28"/>
+      <c r="AU32" s="15"/>
       <c r="AV32" s="15"/>
-      <c r="AW32" s="15"/>
+      <c r="AW32" s="28"/>
       <c r="AX32" s="15"/>
-    </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY32" s="15"/>
+      <c r="AZ32" s="15"/>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -16774,12 +16834,14 @@
       <c r="AR33" s="15"/>
       <c r="AS33" s="15"/>
       <c r="AT33" s="15"/>
-      <c r="AU33" s="28"/>
+      <c r="AU33" s="15"/>
       <c r="AV33" s="15"/>
-      <c r="AW33" s="15"/>
+      <c r="AW33" s="28"/>
       <c r="AX33" s="15"/>
-    </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY33" s="15"/>
+      <c r="AZ33" s="15"/>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -16826,12 +16888,14 @@
       <c r="AR34" s="15"/>
       <c r="AS34" s="15"/>
       <c r="AT34" s="15"/>
-      <c r="AU34" s="28"/>
+      <c r="AU34" s="15"/>
       <c r="AV34" s="15"/>
-      <c r="AW34" s="15"/>
+      <c r="AW34" s="28"/>
       <c r="AX34" s="15"/>
-    </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY34" s="15"/>
+      <c r="AZ34" s="15"/>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -16878,12 +16942,14 @@
       <c r="AR35" s="15"/>
       <c r="AS35" s="15"/>
       <c r="AT35" s="15"/>
-      <c r="AU35" s="28"/>
+      <c r="AU35" s="15"/>
       <c r="AV35" s="15"/>
-      <c r="AW35" s="15"/>
+      <c r="AW35" s="28"/>
       <c r="AX35" s="15"/>
-    </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY35" s="15"/>
+      <c r="AZ35" s="15"/>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -16930,12 +16996,14 @@
       <c r="AR36" s="15"/>
       <c r="AS36" s="15"/>
       <c r="AT36" s="15"/>
-      <c r="AU36" s="28"/>
+      <c r="AU36" s="15"/>
       <c r="AV36" s="15"/>
-      <c r="AW36" s="15"/>
+      <c r="AW36" s="28"/>
       <c r="AX36" s="15"/>
-    </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY36" s="15"/>
+      <c r="AZ36" s="15"/>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -16982,12 +17050,14 @@
       <c r="AR37" s="15"/>
       <c r="AS37" s="15"/>
       <c r="AT37" s="15"/>
-      <c r="AU37" s="28"/>
+      <c r="AU37" s="15"/>
       <c r="AV37" s="15"/>
-      <c r="AW37" s="15"/>
+      <c r="AW37" s="28"/>
       <c r="AX37" s="15"/>
-    </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY37" s="15"/>
+      <c r="AZ37" s="15"/>
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -17034,12 +17104,14 @@
       <c r="AR38" s="15"/>
       <c r="AS38" s="15"/>
       <c r="AT38" s="15"/>
-      <c r="AU38" s="28"/>
+      <c r="AU38" s="15"/>
       <c r="AV38" s="15"/>
-      <c r="AW38" s="15"/>
+      <c r="AW38" s="28"/>
       <c r="AX38" s="15"/>
-    </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY38" s="15"/>
+      <c r="AZ38" s="15"/>
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -17086,12 +17158,14 @@
       <c r="AR39" s="15"/>
       <c r="AS39" s="15"/>
       <c r="AT39" s="15"/>
-      <c r="AU39" s="28"/>
+      <c r="AU39" s="15"/>
       <c r="AV39" s="15"/>
-      <c r="AW39" s="15"/>
+      <c r="AW39" s="28"/>
       <c r="AX39" s="15"/>
-    </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY39" s="15"/>
+      <c r="AZ39" s="15"/>
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -17138,12 +17212,14 @@
       <c r="AR40" s="15"/>
       <c r="AS40" s="15"/>
       <c r="AT40" s="15"/>
-      <c r="AU40" s="28"/>
+      <c r="AU40" s="15"/>
       <c r="AV40" s="15"/>
-      <c r="AW40" s="15"/>
+      <c r="AW40" s="28"/>
       <c r="AX40" s="15"/>
-    </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY40" s="15"/>
+      <c r="AZ40" s="15"/>
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -17190,12 +17266,14 @@
       <c r="AR41" s="15"/>
       <c r="AS41" s="15"/>
       <c r="AT41" s="15"/>
-      <c r="AU41" s="28"/>
+      <c r="AU41" s="15"/>
       <c r="AV41" s="15"/>
-      <c r="AW41" s="15"/>
+      <c r="AW41" s="28"/>
       <c r="AX41" s="15"/>
-    </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY41" s="15"/>
+      <c r="AZ41" s="15"/>
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -17242,12 +17320,14 @@
       <c r="AR42" s="15"/>
       <c r="AS42" s="15"/>
       <c r="AT42" s="15"/>
-      <c r="AU42" s="28"/>
+      <c r="AU42" s="15"/>
       <c r="AV42" s="15"/>
-      <c r="AW42" s="15"/>
+      <c r="AW42" s="28"/>
       <c r="AX42" s="15"/>
-    </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY42" s="15"/>
+      <c r="AZ42" s="15"/>
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -17294,12 +17374,14 @@
       <c r="AR43" s="15"/>
       <c r="AS43" s="15"/>
       <c r="AT43" s="15"/>
-      <c r="AU43" s="28"/>
+      <c r="AU43" s="15"/>
       <c r="AV43" s="15"/>
-      <c r="AW43" s="15"/>
+      <c r="AW43" s="28"/>
       <c r="AX43" s="15"/>
-    </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY43" s="15"/>
+      <c r="AZ43" s="15"/>
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -17346,12 +17428,14 @@
       <c r="AR44" s="15"/>
       <c r="AS44" s="15"/>
       <c r="AT44" s="15"/>
-      <c r="AU44" s="28"/>
+      <c r="AU44" s="15"/>
       <c r="AV44" s="15"/>
-      <c r="AW44" s="15"/>
+      <c r="AW44" s="28"/>
       <c r="AX44" s="15"/>
-    </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY44" s="15"/>
+      <c r="AZ44" s="15"/>
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17398,12 +17482,14 @@
       <c r="AR45" s="15"/>
       <c r="AS45" s="15"/>
       <c r="AT45" s="15"/>
-      <c r="AU45" s="28"/>
+      <c r="AU45" s="15"/>
       <c r="AV45" s="15"/>
-      <c r="AW45" s="15"/>
+      <c r="AW45" s="28"/>
       <c r="AX45" s="15"/>
-    </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY45" s="15"/>
+      <c r="AZ45" s="15"/>
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -17450,12 +17536,14 @@
       <c r="AR46" s="15"/>
       <c r="AS46" s="15"/>
       <c r="AT46" s="15"/>
-      <c r="AU46" s="28"/>
+      <c r="AU46" s="15"/>
       <c r="AV46" s="15"/>
-      <c r="AW46" s="15"/>
+      <c r="AW46" s="28"/>
       <c r="AX46" s="15"/>
-    </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY46" s="15"/>
+      <c r="AZ46" s="15"/>
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -17502,12 +17590,14 @@
       <c r="AR47" s="15"/>
       <c r="AS47" s="15"/>
       <c r="AT47" s="15"/>
-      <c r="AU47" s="28"/>
+      <c r="AU47" s="15"/>
       <c r="AV47" s="15"/>
-      <c r="AW47" s="15"/>
+      <c r="AW47" s="28"/>
       <c r="AX47" s="15"/>
-    </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY47" s="15"/>
+      <c r="AZ47" s="15"/>
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -17554,12 +17644,14 @@
       <c r="AR48" s="15"/>
       <c r="AS48" s="15"/>
       <c r="AT48" s="15"/>
-      <c r="AU48" s="28"/>
+      <c r="AU48" s="15"/>
       <c r="AV48" s="15"/>
-      <c r="AW48" s="15"/>
+      <c r="AW48" s="28"/>
       <c r="AX48" s="15"/>
-    </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY48" s="15"/>
+      <c r="AZ48" s="15"/>
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17606,12 +17698,14 @@
       <c r="AR49" s="15"/>
       <c r="AS49" s="15"/>
       <c r="AT49" s="15"/>
-      <c r="AU49" s="28"/>
+      <c r="AU49" s="15"/>
       <c r="AV49" s="15"/>
-      <c r="AW49" s="15"/>
+      <c r="AW49" s="28"/>
       <c r="AX49" s="15"/>
-    </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY49" s="15"/>
+      <c r="AZ49" s="15"/>
+    </row>
+    <row r="50" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A50" s="17"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -17658,12 +17752,14 @@
       <c r="AR50" s="15"/>
       <c r="AS50" s="15"/>
       <c r="AT50" s="15"/>
-      <c r="AU50" s="28"/>
+      <c r="AU50" s="15"/>
       <c r="AV50" s="15"/>
-      <c r="AW50" s="15"/>
+      <c r="AW50" s="28"/>
       <c r="AX50" s="15"/>
-    </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY50" s="15"/>
+      <c r="AZ50" s="15"/>
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -17710,12 +17806,14 @@
       <c r="AR51" s="15"/>
       <c r="AS51" s="15"/>
       <c r="AT51" s="15"/>
-      <c r="AU51" s="28"/>
+      <c r="AU51" s="15"/>
       <c r="AV51" s="15"/>
-      <c r="AW51" s="15"/>
+      <c r="AW51" s="28"/>
       <c r="AX51" s="15"/>
-    </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="AY51" s="15"/>
+      <c r="AZ51" s="15"/>
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A52" s="17"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -17762,10 +17860,12 @@
       <c r="AR52" s="15"/>
       <c r="AS52" s="15"/>
       <c r="AT52" s="15"/>
-      <c r="AU52" s="28"/>
+      <c r="AU52" s="15"/>
       <c r="AV52" s="15"/>
-      <c r="AW52" s="15"/>
+      <c r="AW52" s="28"/>
       <c r="AX52" s="15"/>
+      <c r="AY52" s="15"/>
+      <c r="AZ52" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -17787,7 +17887,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 AR17:AX52 Y17:AM52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 Y17:AM52 AR17:AS52 AU17:AZ52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -17803,11 +17903,11 @@
     <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AU16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AW16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
     <dataValidation type="list" allowBlank="1" sqref="K17:K103" xr:uid="{FC6EF137-EF73-574C-95CF-B57336C59E8E}">
       <formula1>"column,measure,dimension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L17:L103 AQ17:AQ100" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
+    <dataValidation type="list" allowBlank="1" sqref="L17:L103 AQ17:AQ100 AT17:AT100" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:E14" xr:uid="{D05E7DD6-9150-B941-B705-FF6CFA22D7F9}">
@@ -18971,65 +19071,65 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
     <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="7" width="23.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
-    <col min="9" max="11" width="15.83203125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="2"/>
+    <col min="4" max="8" width="23.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="2" customWidth="1"/>
+    <col min="10" max="12" width="15.83203125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>156</v>
       </c>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I9" s="19" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="20"/>
       <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
@@ -19043,245 +19143,265 @@
         <v>63</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="I10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="15"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="15"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="15"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="15"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="15"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="15"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="15"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="15"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="15"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="15"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="15"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="15"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="15"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="15"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="15"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="15"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="15"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="15"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="15"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="15"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="15"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="15"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="15"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B11:G67 H11:K27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
+    <dataValidation allowBlank="1" sqref="B11:H67 I11:L27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datacontract/templates/excel/odcs-template.xlsx
+++ b/datacontract/templates/excel/odcs-template.xlsx
@@ -1,40 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fb/IdeaProjects/entropy-data/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AEC928-3B3E-6A48-BC07-BADEA98D1A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="13_ncr:1_{C1AEC928-3B3E-6A48-BC07-BADEA98D1A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F5590A4-3B23-4E28-B28D-64EB35E306A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
     <sheet name="Fundamentals" sheetId="10" r:id="rId2"/>
     <sheet name="Schema &lt;table_name&gt;" sheetId="3" r:id="rId3"/>
     <sheet name="Relationships" sheetId="23" r:id="rId4"/>
-    <sheet name="Quality" sheetId="21" r:id="rId5"/>
-    <sheet name="Support" sheetId="12" r:id="rId6"/>
-    <sheet name="Team" sheetId="13" r:id="rId7"/>
-    <sheet name="Roles" sheetId="16" r:id="rId8"/>
-    <sheet name="SLA" sheetId="17" r:id="rId9"/>
-    <sheet name="Servers" sheetId="20" r:id="rId10"/>
-    <sheet name="Pricing" sheetId="15" r:id="rId11"/>
-    <sheet name="Custom Properties" sheetId="11" r:id="rId12"/>
+    <sheet name="Enums" sheetId="26" r:id="rId5"/>
+    <sheet name="Synonyms" sheetId="27" r:id="rId6"/>
+    <sheet name="Verified Statements" sheetId="28" r:id="rId7"/>
+    <sheet name="Constraints" sheetId="29" r:id="rId8"/>
+    <sheet name="Quality" sheetId="21" r:id="rId9"/>
+    <sheet name="Support" sheetId="12" r:id="rId10"/>
+    <sheet name="Team" sheetId="13" r:id="rId11"/>
+    <sheet name="Roles" sheetId="16" r:id="rId12"/>
+    <sheet name="SLA" sheetId="17" r:id="rId13"/>
+    <sheet name="Servers" sheetId="20" r:id="rId14"/>
+    <sheet name="Pricing" sheetId="15" r:id="rId15"/>
+    <sheet name="Custom Properties" sheetId="11" r:id="rId16"/>
+    <sheet name="Authoritative Definitions" sheetId="25" r:id="rId17"/>
+    <sheet name="_ServerFields" sheetId="24" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
+    <definedName name="_ServerFieldLabels">_ServerFields!$A$2:$A$24</definedName>
+    <definedName name="_ServerFieldMatrix">_ServerFields!$B$2:$AS$24</definedName>
+    <definedName name="_ServerTypes">_ServerFields!$B$1:$AS$1</definedName>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
-    <definedName name="CustomProperties">'Custom Properties'!$A$5:$B$21</definedName>
+    <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$Z$1000</definedName>
+    <definedName name="constraints">Constraints!$A$4:$Z$1000</definedName>
+    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
+    <definedName name="CustomProperties">'Custom Properties'!$A$4:$H$1000</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
     <definedName name="dataProduct">Fundamentals!$C$15</definedName>
     <definedName name="description.limitations">Fundamentals!$C$20</definedName>
     <definedName name="description.purpose">Fundamentals!$C$19</definedName>
     <definedName name="description.usage">Fundamentals!$C$21</definedName>
     <definedName name="domain">Fundamentals!$C$14</definedName>
+    <definedName name="enum">Enums!$A$4:$Z$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
@@ -45,84 +58,67 @@
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
     <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$A$4:$E$1000</definedName>
+    <definedName name="roles" localSheetId="11">Roles!$A$4:$Z$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
+    <definedName name="schema.context.instructions" localSheetId="2">'Schema &lt;table_name&gt;'!$B$14</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
+    <definedName name="schema.deprecated" localSheetId="2">'Schema &lt;table_name&gt;'!$B$13</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema &lt;table_name&gt;'!$B$7</definedName>
+    <definedName name="schema.id" localSheetId="2">'Schema &lt;table_name&gt;'!$B$12</definedName>
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$13:$L$981</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AZ$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
-    <definedName name="servers.azure.delimiter">Servers!$C$14</definedName>
-    <definedName name="servers.azure.format">Servers!$C$13</definedName>
-    <definedName name="servers.azure.location">Servers!$C$12</definedName>
-    <definedName name="servers.bigquery.dataset">Servers!$C$18</definedName>
-    <definedName name="servers.bigquery.project">Servers!$C$17</definedName>
-    <definedName name="servers.custom.account">Servers!$C$67</definedName>
-    <definedName name="servers.custom.catalog">Servers!$C$68</definedName>
-    <definedName name="servers.custom.database">Servers!$C$69</definedName>
-    <definedName name="servers.custom.dataset">Servers!$C$70</definedName>
-    <definedName name="servers.custom.delimiter">Servers!$C$71</definedName>
-    <definedName name="servers.custom.endpointUrl">Servers!$C$72</definedName>
-    <definedName name="servers.custom.format">Servers!$C$73</definedName>
-    <definedName name="servers.custom.host">Servers!$C$74</definedName>
-    <definedName name="servers.custom.location">Servers!$C$75</definedName>
-    <definedName name="servers.custom.path">Servers!$C$76</definedName>
-    <definedName name="servers.custom.port">Servers!$C$77</definedName>
-    <definedName name="servers.custom.project">Servers!$C$78</definedName>
-    <definedName name="servers.custom.region">Servers!$C$79</definedName>
-    <definedName name="servers.custom.regionName">Servers!$C$80</definedName>
-    <definedName name="servers.custom.schema">Servers!$C$81</definedName>
-    <definedName name="servers.custom.serviceName">Servers!$C$82</definedName>
-    <definedName name="servers.custom.stagingDir">Servers!$C$83</definedName>
-    <definedName name="servers.custom.stream">Servers!$C$84</definedName>
-    <definedName name="servers.custom.warehouse">Servers!$C$85</definedName>
-    <definedName name="servers.databricks.catalog">Servers!$C$21</definedName>
-    <definedName name="servers.databricks.host">Servers!$C$23</definedName>
-    <definedName name="servers.databricks.schema">Servers!$C$22</definedName>
+    <definedName name="servers.account">Servers!$C$11</definedName>
+    <definedName name="servers.catalog">Servers!$C$12</definedName>
+    <definedName name="servers.catalogUrl">Servers!$C$13</definedName>
+    <definedName name="servers.database">Servers!$C$14</definedName>
+    <definedName name="servers.dataset">Servers!$C$15</definedName>
+    <definedName name="servers.delimiter">Servers!$C$16</definedName>
     <definedName name="servers.description">Servers!$C$6</definedName>
+    <definedName name="servers.encoding">Servers!$C$17</definedName>
+    <definedName name="servers.endpointUrl">Servers!$C$18</definedName>
     <definedName name="servers.environment">Servers!$C$5</definedName>
-    <definedName name="servers.glue.account">Servers!$C$26</definedName>
-    <definedName name="servers.glue.database">Servers!$C$27</definedName>
-    <definedName name="servers.glue.format">Servers!$C$29</definedName>
-    <definedName name="servers.glue.location">Servers!$C$28</definedName>
-    <definedName name="servers.kafka.format">Servers!$C$33</definedName>
-    <definedName name="servers.kafka.host">Servers!$C$32</definedName>
-    <definedName name="servers.oracle.host">Servers!$C$62</definedName>
-    <definedName name="servers.oracle.port">Servers!$C$63</definedName>
-    <definedName name="servers.oracle.servicename">Servers!$C$64</definedName>
-    <definedName name="servers.postgres.database">Servers!$C$38</definedName>
-    <definedName name="servers.postgres.host">Servers!$C$36</definedName>
-    <definedName name="servers.postgres.port">Servers!$C$37</definedName>
-    <definedName name="servers.postgres.schema">Servers!$C$39</definedName>
-    <definedName name="servers.s3.delimiter">Servers!$C$45</definedName>
-    <definedName name="servers.s3.endpointUrl">Servers!$C$43</definedName>
-    <definedName name="servers.s3.format">Servers!$C$44</definedName>
-    <definedName name="servers.s3.location">Servers!$C$42</definedName>
+    <definedName name="servers.format">Servers!$C$19</definedName>
+    <definedName name="servers.host">Servers!$C$20</definedName>
+    <definedName name="servers.id">Servers!$C$35</definedName>
+    <definedName name="servers.location">Servers!$C$21</definedName>
+    <definedName name="servers.namespace">Servers!$C$22</definedName>
+    <definedName name="servers.path">Servers!$C$23</definedName>
+    <definedName name="servers.port">Servers!$C$24</definedName>
+    <definedName name="servers.project">Servers!$C$25</definedName>
+    <definedName name="servers.region">Servers!$C$26</definedName>
+    <definedName name="servers.regionName">Servers!$C$27</definedName>
+    <definedName name="servers.schema">Servers!$C$28</definedName>
     <definedName name="servers.server">Servers!$C$4</definedName>
-    <definedName name="servers.snowflake.account">Servers!$C$50</definedName>
-    <definedName name="servers.snowflake.database">Servers!$C$51</definedName>
-    <definedName name="servers.snowflake.host">Servers!$C$48</definedName>
-    <definedName name="servers.snowflake.port">Servers!$C$49</definedName>
-    <definedName name="servers.snowflake.schema">Servers!$C$53</definedName>
-    <definedName name="servers.snowflake.warehouse">Servers!$C$52</definedName>
-    <definedName name="servers.sqlserver.database">Servers!$C$58</definedName>
-    <definedName name="servers.sqlserver.host">Servers!$C$56</definedName>
-    <definedName name="servers.sqlserver.port">Servers!$C$57</definedName>
-    <definedName name="servers.sqlserver.schema">Servers!$C$59</definedName>
+    <definedName name="servers.serviceName">Servers!$C$29</definedName>
+    <definedName name="servers.stagingDir">Servers!$C$30</definedName>
+    <definedName name="servers.stream">Servers!$C$31</definedName>
     <definedName name="servers.type">Servers!$C$8</definedName>
+    <definedName name="servers.warehouse">Servers!$C$32</definedName>
+    <definedName name="servers.workgroup">Servers!$C$33</definedName>
     <definedName name="slaDefaultElement">SLA!$B$4</definedName>
-    <definedName name="slaProperties" localSheetId="8">SLA!$A$6:$F$1002</definedName>
+    <definedName name="slaProperties" localSheetId="12">SLA!$A$6:$Z$1002</definedName>
     <definedName name="status">Fundamentals!$C$10</definedName>
-    <definedName name="support">Support!$A$4:$F$1000</definedName>
+    <definedName name="support">Support!$A$4:$Z$1000</definedName>
+    <definedName name="synonyms">Synonyms!$A$4:$Z$1000</definedName>
     <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="team">Team!$A$4:$G$1000</definedName>
+    <definedName name="team">Team!$A$9:$Z$1000</definedName>
+    <definedName name="team.description">Team!$B$5</definedName>
+    <definedName name="team.id">Team!$B$7</definedName>
+    <definedName name="team.name">Team!$B$4</definedName>
+    <definedName name="team.tags">Team!$B$6</definedName>
+    <definedName name="templateVersion">Instructions!$B$29</definedName>
     <definedName name="tenant">Fundamentals!$C$16</definedName>
+    <definedName name="verifiedStatements">'Verified Statements'!$A$4:$Z$1000</definedName>
     <definedName name="version">Fundamentals!$C$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -139,183 +135,381 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="242">
+  <si>
+    <t>Open Data Contract Standard V3</t>
+  </si>
+  <si>
+    <t>Use this Excel template to edit data contracts.</t>
+  </si>
+  <si>
+    <t>Data Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A data contract is a document that defines the structure, format, semantics, quality, and terms of use </t>
+  </si>
+  <si>
+    <t xml:space="preserve">for exchanging data between a data provider and their consumers. </t>
+  </si>
+  <si>
+    <t>A data contract is usually defined in YAML, but you can use this Excel document for easier collaboration</t>
+  </si>
+  <si>
+    <t>with your stakeholders.</t>
+  </si>
+  <si>
+    <t>Instructions</t>
+  </si>
+  <si>
+    <t>1. Fill in the 'Fundamentals' sheet with basic contract information</t>
+  </si>
+  <si>
+    <t>2. For every table create a Sheet called "Schema &lt;tablename&gt;"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. After completing the template, </t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t>Convert  to YAML using Data Contract CLI</t>
+  </si>
+  <si>
+    <t>datacontract import --format excel --source odcs.xlsx</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>Or, if you use Entropy Data, import the Excel directly.</t>
+  </si>
+  <si>
+    <t>Existing data contracts with the same ID will be updated.</t>
+  </si>
+  <si>
+    <t>Open Entropy Data → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
+  </si>
+  <si>
+    <t>Authors:</t>
+  </si>
+  <si>
+    <t>Jochen Christ, Dr. Simon Harrer</t>
+  </si>
+  <si>
+    <t>Version:</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>License:</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t>Template Version:</t>
+  </si>
+  <si>
+    <t>Fundamentals</t>
+  </si>
+  <si>
+    <t>This section describes the data model for one table, message, or object with their properties.</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>DataContract</t>
+  </si>
+  <si>
+    <t>apiVersion</t>
+  </si>
+  <si>
+    <t>v3.2.0</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Data Product</t>
+  </si>
+  <si>
+    <t>Tenant</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Limitations</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Context (Guidance for AI)</t>
+  </si>
+  <si>
+    <t>Schema</t>
+  </si>
+  <si>
+    <t>Copy this sheet for every model in your data contract.</t>
+  </si>
+  <si>
+    <t>&lt;table_name&gt;</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>Business Name</t>
+  </si>
+  <si>
+    <t>Physical Name</t>
+  </si>
+  <si>
+    <t>Data Granularity</t>
+  </si>
+  <si>
+    <t>Deprecated</t>
+  </si>
+  <si>
+    <t>Logical Type Options</t>
+  </si>
+  <si>
+    <t>Custom Properties (add as needed)</t>
+  </si>
   <si>
     <t>Property</t>
   </si>
   <si>
+    <t>Logical Type</t>
+  </si>
+  <si>
+    <t>Physical Type</t>
+  </si>
+  <si>
+    <t>Example(s)</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Unique</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Semantic Type</t>
+  </si>
+  <si>
+    <t>Authoritative Definition URL</t>
+  </si>
+  <si>
+    <t>Authoritative Definition Type</t>
+  </si>
+  <si>
+    <t>Primary Key</t>
+  </si>
+  <si>
+    <t>Primary Key Position</t>
+  </si>
+  <si>
+    <t>Partitioned</t>
+  </si>
+  <si>
+    <t>Partition Key Position</t>
+  </si>
+  <si>
+    <t>Encrypted Name</t>
+  </si>
+  <si>
+    <t>Transform Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform Logic	</t>
+  </si>
+  <si>
+    <t>Transform Description</t>
+  </si>
+  <si>
+    <t>Critical Data Element Status</t>
+  </si>
+  <si>
+    <t>Maximum Items</t>
+  </si>
+  <si>
+    <t>Minimum Items</t>
+  </si>
+  <si>
+    <t>Unique Items</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Minimum Length</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Exclusive Minimum</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Exclusive Maximum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Multiple Of</t>
+  </si>
+  <si>
+    <t>Minimum Properties</t>
+  </si>
+  <si>
+    <t>Maximum Properties</t>
+  </si>
+  <si>
+    <t>Required Properties</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Comments (internal)</t>
+  </si>
+  <si>
+    <t>Relationships</t>
+  </si>
+  <si>
+    <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
+  </si>
+  <si>
+    <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Enums</t>
+  </si>
+  <si>
+    <t>Restrict the allowed values of a property. Use one row per accepted value.</t>
+  </si>
+  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>DataContract</t>
-  </si>
-  <si>
-    <t>apiVersion</t>
-  </si>
-  <si>
-    <t>Logical Type</t>
-  </si>
-  <si>
-    <t>Physical Type</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Business Name</t>
-  </si>
-  <si>
-    <t>Example(s)</t>
-  </si>
-  <si>
-    <t>Classification</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Authoritative Definition URL</t>
-  </si>
-  <si>
-    <t>Authoritative Definition Type</t>
-  </si>
-  <si>
-    <t>Unique</t>
-  </si>
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>Schema</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>This section describes the data model for one table, message, or object with their properties.</t>
-  </si>
-  <si>
-    <t>Fundamentals</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Domain</t>
-  </si>
-  <si>
-    <t>Data Product</t>
-  </si>
-  <si>
-    <t>Tenant</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Limitations</t>
-  </si>
-  <si>
-    <t>Usage</t>
-  </si>
-  <si>
-    <t>Custom Properties</t>
-  </si>
-  <si>
-    <t>This section covers custom properties you may find in a data contract.</t>
-  </si>
-  <si>
-    <t>Open Data Contract Standard V3</t>
-  </si>
-  <si>
-    <t>Instructions</t>
-  </si>
-  <si>
-    <t>1. Fill in the 'Fundamentals' sheet with basic contract information</t>
-  </si>
-  <si>
-    <t>2. For every table create a Sheet called "Schema &lt;tablename&gt;"</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Version:</t>
-  </si>
-  <si>
-    <t>Authors:</t>
-  </si>
-  <si>
-    <t>Jochen Christ, Dr. Simon Harrer</t>
-  </si>
-  <si>
-    <t>License:</t>
-  </si>
-  <si>
-    <t>MIT</t>
-  </si>
-  <si>
-    <t>Data Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data contract is a document that defines the structure, format, semantics, quality, and terms of use </t>
-  </si>
-  <si>
-    <t xml:space="preserve">for exchanging data between a data provider and their consumers. </t>
-  </si>
-  <si>
-    <t>Use this Excel template to edit data contracts.</t>
-  </si>
-  <si>
-    <t>A data contract is usually defined in YAML, but you can use this Excel document for easier collaboration</t>
-  </si>
-  <si>
-    <t>with your stakeholders.</t>
-  </si>
-  <si>
-    <t>owner</t>
-  </si>
-  <si>
-    <t>Copy this sheet for every model in your data contract.</t>
-  </si>
-  <si>
-    <t>&lt;table_name&gt;</t>
-  </si>
-  <si>
-    <t>Physical Name</t>
-  </si>
-  <si>
-    <t>Data Granularity</t>
-  </si>
-  <si>
-    <t>Channel</t>
-  </si>
-  <si>
-    <t>Tool</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Channel URL</t>
-  </si>
-  <si>
-    <t>Invitation URL</t>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Synonyms</t>
+  </si>
+  <si>
+    <t>Alternative names for a schema or a property. Leave Property blank for a synonym of the schema itself.</t>
+  </si>
+  <si>
+    <t>Synonym</t>
+  </si>
+  <si>
+    <t>Locale</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Verified Statements</t>
+  </si>
+  <si>
+    <t>Verified question/answer pairs that give consumers and AI agents context. Level: Contract or Schema.</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Constraints that consumers and AI agents must respect when using the data. Level: Contract or Schema.</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Add quality rules to the schemas of the contract or their properties.</t>
+  </si>
+  <si>
+    <t>Quality Type</t>
+  </si>
+  <si>
+    <t>Rule (Library)</t>
+  </si>
+  <si>
+    <t>Query (SQL)</t>
+  </si>
+  <si>
+    <t>Threshold Operator</t>
+  </si>
+  <si>
+    <t>Threshold Value</t>
+  </si>
+  <si>
+    <t>Quality Engine (Custom)</t>
+  </si>
+  <si>
+    <t>Implementation (Custom)</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Scheduler</t>
+  </si>
+  <si>
+    <t>Schedule</t>
   </si>
   <si>
     <t>Support and Communication Channels</t>
@@ -325,6 +519,21 @@
 Support and communication channels help consumers find help regarding their use of the data contract.</t>
   </si>
   <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Channel URL</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Invitation URL</t>
+  </si>
+  <si>
     <t>Team</t>
   </si>
   <si>
@@ -332,6 +541,18 @@
 </t>
   </si>
   <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Team Description</t>
+  </si>
+  <si>
+    <t>Team Tags</t>
+  </si>
+  <si>
+    <t>Team ID</t>
+  </si>
+  <si>
     <t>Username</t>
   </si>
   <si>
@@ -345,88 +566,6 @@
   </si>
   <si>
     <t>Replaced By Username</t>
-  </si>
-  <si>
-    <t>Partitioned</t>
-  </si>
-  <si>
-    <t>Primary Key</t>
-  </si>
-  <si>
-    <t>Primary Key Position</t>
-  </si>
-  <si>
-    <t>Partition Key Position</t>
-  </si>
-  <si>
-    <t>Encrypted Name</t>
-  </si>
-  <si>
-    <t>Transform Sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transform Logic	</t>
-  </si>
-  <si>
-    <t>Transform Description</t>
-  </si>
-  <si>
-    <t>Critical Data Element Status</t>
-  </si>
-  <si>
-    <t>Maximum Items</t>
-  </si>
-  <si>
-    <t>Logical Type Options</t>
-  </si>
-  <si>
-    <t>Minimum Items</t>
-  </si>
-  <si>
-    <t>Unique Items</t>
-  </si>
-  <si>
-    <t>Format</t>
-  </si>
-  <si>
-    <t>Exclusive Maximum</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>Minimum</t>
-  </si>
-  <si>
-    <t>Multiple Of</t>
-  </si>
-  <si>
-    <t>Maximum Properties</t>
-  </si>
-  <si>
-    <t>Minimum Properties</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Quality Type</t>
-  </si>
-  <si>
-    <t>Pricing</t>
-  </si>
-  <si>
-    <t>Price Amount</t>
-  </si>
-  <si>
-    <t>Price Currency</t>
-  </si>
-  <si>
-    <t>Price Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
-</t>
   </si>
   <si>
     <t>Roles</t>
@@ -481,12 +620,18 @@
     <t>Environment</t>
   </si>
   <si>
+    <t>Connection</t>
+  </si>
+  <si>
     <t>Account</t>
   </si>
   <si>
     <t>Catalog</t>
   </si>
   <si>
+    <t>Catalog URL</t>
+  </si>
+  <si>
     <t>Database</t>
   </si>
   <si>
@@ -496,6 +641,9 @@
     <t>Delimiter</t>
   </si>
   <si>
+    <t>Encoding</t>
+  </si>
+  <si>
     <t>Endpoint URL</t>
   </si>
   <si>
@@ -505,6 +653,9 @@
     <t>Location</t>
   </si>
   <si>
+    <t>Namespace</t>
+  </si>
+  <si>
     <t>Path</t>
   </si>
   <si>
@@ -520,155 +671,210 @@
     <t>Region Name</t>
   </si>
   <si>
-    <t>Databricks Server</t>
-  </si>
-  <si>
-    <t>Azure</t>
-  </si>
-  <si>
-    <t>Amazon Glue</t>
-  </si>
-  <si>
-    <t>Kafka</t>
-  </si>
-  <si>
-    <t>PostgreSQL</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>Snowflake</t>
+    <t>Service Name</t>
+  </si>
+  <si>
+    <t>Staging Directory</t>
+  </si>
+  <si>
+    <t>Stream</t>
   </si>
   <si>
     <t>Warehouse</t>
   </si>
   <si>
-    <t>SQL Server</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>Service Name</t>
-  </si>
-  <si>
-    <t>Staging Directory</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>BigQuery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. After completing the template, </t>
-  </si>
-  <si>
-    <t>a)</t>
-  </si>
-  <si>
-    <t>Convert  to YAML using Data Contract CLI</t>
-  </si>
-  <si>
-    <t>b)</t>
-  </si>
-  <si>
-    <t>Required Properties</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Minimum Length</t>
-  </si>
-  <si>
-    <t>Exclusive Minimum</t>
-  </si>
-  <si>
-    <t>datacontract import --format excel --source odcs.xlsx</t>
-  </si>
-  <si>
-    <t>Existing data contracts with the same ID will be updated.</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>This section describes data quality rules &amp; parameters. They are tightly linked to the schema described in the previous sheet(s).</t>
-  </si>
-  <si>
-    <t>Threshold Operator</t>
-  </si>
-  <si>
-    <t>Threshold Value</t>
-  </si>
-  <si>
-    <t>Implementation (Custom)</t>
-  </si>
-  <si>
-    <t>Query (SQL)</t>
-  </si>
-  <si>
-    <t>Quality Engine (Custom)</t>
-  </si>
-  <si>
-    <t>Rule (Library)</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Scheduler</t>
-  </si>
-  <si>
-    <t>Schedule</t>
-  </si>
-  <si>
-    <t>Comments (internal)</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>Or, if you use Entropy Data, import the Excel directly.</t>
-  </si>
-  <si>
-    <t>Open Entropy Data → Go to Data Contracts → Click Add Data Contract → Import from Excel</t>
-  </si>
-  <si>
-    <t>Oracle</t>
-  </si>
-  <si>
-    <t>ServiceName</t>
-  </si>
-  <si>
-    <t>v3.0.2</t>
-  </si>
-  <si>
-    <t>Relationships</t>
-  </si>
-  <si>
-    <t>Define relationships between schemas by mapping properties from one schema to another (e.g., foreign keys).</t>
-  </si>
-  <si>
-    <t>Use schema.property dot syntax (e.g., orders.customer_id). Comma-separated for composite keys. Level: 'schema' or 'property'.</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
+    <t>Workgroup</t>
+  </si>
+  <si>
+    <t>Pricing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This section covers pricing when you bill your customer for using this data product.
+</t>
+  </si>
+  <si>
+    <t>Price Amount</t>
+  </si>
+  <si>
+    <t>Price Currency</t>
+  </si>
+  <si>
+    <t>Price Unit</t>
+  </si>
+  <si>
+    <t>Custom Properties</t>
+  </si>
+  <si>
+    <t>Store additional information about the contract or specific elements of it. This is more fine-grained than the columns for Custom Properties on other sheets.</t>
+  </si>
+  <si>
+    <t>Element Type</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>Authoritative Definitions</t>
+  </si>
+  <si>
+    <t>Links to authoritative sources (business definitions, implementations, tutorials) for any element of the contract.</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>api</t>
+  </si>
+  <si>
+    <t>athena</t>
+  </si>
+  <si>
+    <t>azure</t>
+  </si>
+  <si>
+    <t>bigquery</t>
+  </si>
+  <si>
+    <t>btrieve</t>
+  </si>
+  <si>
+    <t>clickhouse</t>
+  </si>
+  <si>
+    <t>databricks</t>
+  </si>
+  <si>
+    <t>denodo</t>
+  </si>
+  <si>
+    <t>dremio</t>
+  </si>
+  <si>
+    <t>duckdb</t>
+  </si>
+  <si>
+    <t>exasol</t>
+  </si>
+  <si>
+    <t>fastobjects</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>hana</t>
+  </si>
+  <si>
+    <t>cloudsql</t>
+  </si>
+  <si>
+    <t>db2</t>
+  </si>
+  <si>
+    <t>hive</t>
+  </si>
+  <si>
+    <t>iceberg</t>
+  </si>
+  <si>
+    <t>impala</t>
+  </si>
+  <si>
+    <t>informix</t>
+  </si>
+  <si>
+    <t>ingres</t>
+  </si>
+  <si>
+    <t>kafka</t>
+  </si>
+  <si>
+    <t>kinesis</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>mysql</t>
+  </si>
+  <si>
+    <t>oracle</t>
+  </si>
+  <si>
+    <t>poet</t>
+  </si>
+  <si>
+    <t>postgresql</t>
+  </si>
+  <si>
+    <t>postgres</t>
+  </si>
+  <si>
+    <t>presto</t>
+  </si>
+  <si>
+    <t>pubsub</t>
+  </si>
+  <si>
+    <t>redshift</t>
+  </si>
+  <si>
+    <t>s3</t>
+  </si>
+  <si>
+    <t>sftp</t>
+  </si>
+  <si>
+    <t>snowflake</t>
+  </si>
+  <si>
+    <t>sqlserver</t>
+  </si>
+  <si>
+    <t>synapse</t>
+  </si>
+  <si>
+    <t>teradata</t>
+  </si>
+  <si>
+    <t>trino</t>
+  </si>
+  <si>
+    <t>vectorwise</t>
+  </si>
+  <si>
+    <t>versant</t>
+  </si>
+  <si>
+    <t>vertica</t>
+  </si>
+  <si>
+    <t>zen</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,7 +926,7 @@
       <name val="Aptos Mono"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -754,12 +960,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCBD5E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,7 +1081,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -948,9 +1148,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -966,6 +1163,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -984,15 +1182,42 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1387,46 +1612,51 @@
   <we:properties/>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
 </we:webextension>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.83203125" style="3"/>
+    <col min="2" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="24">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="15.95">
       <c r="A2" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="15.95">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="15.95">
       <c r="A7" s="12" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1437,9 +1667,9 @@
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
     </row>
-    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="15.95">
       <c r="A8" s="13" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1450,9 +1680,9 @@
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
     </row>
-    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15.95">
       <c r="A9" s="13" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1463,9 +1693,9 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="15.95">
       <c r="A10" s="13" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1476,9 +1706,9 @@
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="15.95">
       <c r="A11" s="13" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -1489,7 +1719,7 @@
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="15.95">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -1500,7 +1730,7 @@
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="15.95">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1511,9 +1741,9 @@
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="15.95">
       <c r="A14" s="12" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -1524,9 +1754,9 @@
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15.95">
       <c r="A15" s="13" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1537,9 +1767,9 @@
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15.95">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -1550,9 +1780,9 @@
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15.95">
       <c r="A17" s="13" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -1563,12 +1793,12 @@
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15.95">
       <c r="A18" s="23" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1578,10 +1808,10 @@
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
     </row>
-    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15.95">
       <c r="A19" s="23"/>
       <c r="B19" s="24" t="s">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -1591,7 +1821,7 @@
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
     </row>
-    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15.95">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -1602,12 +1832,12 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
     </row>
-    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15.95">
       <c r="A21" s="25" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>161</v>
+        <v>15</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1617,10 +1847,10 @@
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15.95">
       <c r="A22" s="25"/>
       <c r="B22" s="13" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -1630,10 +1860,10 @@
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
     </row>
-    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15.95">
       <c r="A23" s="13"/>
       <c r="B23" s="13" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -1643,7 +1873,7 @@
       <c r="H23" s="13"/>
       <c r="I23" s="13"/>
     </row>
-    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15.95">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -1654,7 +1884,7 @@
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
     </row>
-    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15.95">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -1665,12 +1895,12 @@
       <c r="H25" s="13"/>
       <c r="I25" s="13"/>
     </row>
-    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15.95">
       <c r="A26" s="13" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1680,12 +1910,12 @@
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
     </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15.95">
       <c r="A27" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>160</v>
+        <v>20</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>21</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1695,12 +1925,12 @@
       <c r="H27" s="13"/>
       <c r="I27" s="13"/>
     </row>
-    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15.95">
       <c r="A28" s="13" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -1710,9 +1940,13 @@
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
     </row>
-    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
+    <row r="29" spans="1:9" ht="15.95">
+      <c r="A29" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="14">
+        <v>2</v>
+      </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -1721,7 +1955,7 @@
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
     </row>
-    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15.95">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1732,7 +1966,7 @@
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
     </row>
-    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15.95">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -1750,34 +1984,1156 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{246082EA-DAAB-1649-871C-B98419509DC8}">
-  <dimension ref="A1:F85"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB3633-F435-1B44-A99B-F400ACF77C57}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.1640625" style="2" customWidth="1"/>
-    <col min="3" max="6" width="36.1640625" style="2" customWidth="1"/>
-    <col min="7" max="22" width="15" style="2" customWidth="1"/>
-    <col min="23" max="30" width="32.83203125" style="2" customWidth="1"/>
-    <col min="31" max="31" width="34.6640625" style="2" customWidth="1"/>
-    <col min="32" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
+    <col min="4" max="6" width="23.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" style="2" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="24">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75">
+      <c r="A2" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.95" customHeight="1">
+      <c r="H3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" sqref="B5:F61" xr:uid="{19A11CF7-5A67-E844-8CDE-E9312B26965E}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="59.7109375" style="2" customWidth="1"/>
+    <col min="4" max="7" width="23.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" style="2" customWidth="1"/>
+    <col min="9" max="11" width="26.7109375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="24">
+      <c r="A1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75">
+      <c r="A4" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75">
+      <c r="A5" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75">
+      <c r="A6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75">
+      <c r="A7" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.95" customHeight="1">
+      <c r="I8" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75">
+      <c r="A9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I8:K8"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" sqref="B10:G66" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" style="2" customWidth="1"/>
+    <col min="7" max="9" width="26.7109375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="24">
+      <c r="A1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75">
+      <c r="A2" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.95" customHeight="1">
+      <c r="G3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" sqref="B5:E61" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C18618-CA09-244F-9E12-D5D128AED5CE}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="32.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" style="2" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24">
+      <c r="A1" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.95" customHeight="1">
+      <c r="H5" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H5:J5"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" sqref="B7:F63" xr:uid="{7F4EE529-7BE7-6547-817C-8DBC88D35FEC}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B4" xr:uid="{8220F424-DC29-F648-BD41-E75C77AE8B05}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{246082EA-DAAB-1649-871C-B98419509DC8}">
+  <dimension ref="A1:Z85"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="2" customWidth="1"/>
+    <col min="3" max="6" width="36.140625" style="2" customWidth="1"/>
+    <col min="7" max="22" width="15" style="2" customWidth="1"/>
+    <col min="23" max="30" width="32.85546875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="34.7109375" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="8.85546875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="24">
+      <c r="A1" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26">
       <c r="A2" s="4" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26">
       <c r="A4" s="7" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="5"/>
@@ -1785,9 +3141,9 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26">
       <c r="A5" s="7" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5"/>
@@ -1795,9 +3151,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26">
       <c r="A6" s="7" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="5"/>
@@ -1805,13 +3161,13 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="5"/>
@@ -1819,678 +3175,894 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
+    <row r="10" spans="1:26" ht="15.75">
+      <c r="A10" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75">
+      <c r="B11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75">
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75">
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75">
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75">
+      <c r="B15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75">
+      <c r="B16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+    </row>
+    <row r="17" spans="2:26" ht="15.75">
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+    </row>
+    <row r="18" spans="2:26" ht="15.75">
       <c r="B18" s="2" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="7"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+    </row>
+    <row r="19" spans="2:26" ht="15.75">
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+    </row>
+    <row r="20" spans="2:26" ht="15.75">
+      <c r="B20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+    </row>
+    <row r="21" spans="2:26" ht="15.75">
       <c r="B21" s="2" t="s">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="7"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+    </row>
+    <row r="22" spans="2:26" ht="15.75">
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="7"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+    </row>
+    <row r="23" spans="2:26" ht="15.75">
       <c r="B23" s="2" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+    </row>
+    <row r="24" spans="2:26" ht="15.75">
+      <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+    </row>
+    <row r="25" spans="2:26" ht="15.75">
+      <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+    </row>
+    <row r="26" spans="2:26" ht="15.75">
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+    </row>
+    <row r="27" spans="2:26" ht="15.75">
       <c r="B27" s="2" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+    </row>
+    <row r="28" spans="2:26" ht="15.75">
       <c r="B28" s="2" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+    </row>
+    <row r="29" spans="2:26" ht="15.75">
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="7"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+    </row>
+    <row r="30" spans="2:26" ht="15.75">
+      <c r="B30" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+    </row>
+    <row r="31" spans="2:26" ht="15.75">
+      <c r="B31" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+    </row>
+    <row r="32" spans="2:26" ht="15.75">
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="7"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+    </row>
+    <row r="33" spans="1:26" ht="15.75">
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+    </row>
+    <row r="34" spans="1:26" ht="15.75"/>
+    <row r="35" spans="1:26" ht="15.75">
+      <c r="B35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+    </row>
+    <row r="36" spans="1:26" ht="15.75">
+      <c r="A36" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="15.75">
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="7"/>
-      <c r="B38" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+    </row>
+    <row r="38" spans="1:26" ht="15.75">
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="7"/>
-      <c r="B39" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+    </row>
+    <row r="39" spans="1:26" ht="15.75">
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="7"/>
-      <c r="B42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="7"/>
-      <c r="B43" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="7"/>
-      <c r="B44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="7"/>
-      <c r="B45" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="7"/>
-      <c r="B48" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="7"/>
-      <c r="B49" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="7"/>
-      <c r="B50" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="7"/>
-      <c r="B51" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="7"/>
-      <c r="B52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="7"/>
-      <c r="B56" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="7"/>
-      <c r="B57" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
-      <c r="B58" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="7"/>
-      <c r="B59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="7"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="7"/>
-      <c r="B62" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="7"/>
-      <c r="B64" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="7"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="7"/>
-      <c r="B68" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="7"/>
-      <c r="B69" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="7"/>
-      <c r="B70" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="7"/>
-      <c r="B71" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="7"/>
-      <c r="B72" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="7"/>
-      <c r="B73" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="7"/>
-      <c r="B74" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="7"/>
-      <c r="B75" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="7"/>
-      <c r="B76" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="7"/>
-      <c r="B77" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="7"/>
-      <c r="B78" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="7"/>
-      <c r="B79" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="7"/>
-      <c r="B80" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="7"/>
-      <c r="B81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="7"/>
-      <c r="B82" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="7"/>
-      <c r="B83" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="7"/>
-      <c r="B84" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="7"/>
-      <c r="B85" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-    </row>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+    </row>
+    <row r="40" spans="1:26" ht="15.75"/>
+    <row r="41" spans="1:26" ht="15.75"/>
+    <row r="42" spans="1:26" ht="15.75"/>
+    <row r="43" spans="1:26" ht="15.75"/>
+    <row r="44" spans="1:26" ht="15.75"/>
+    <row r="45" spans="1:26" ht="15.75"/>
+    <row r="46" spans="1:26" ht="15.75"/>
+    <row r="47" spans="1:26" ht="15.75"/>
+    <row r="48" spans="1:26" ht="15.75"/>
+    <row r="49" ht="15.75"/>
+    <row r="50" ht="15.75"/>
+    <row r="51" ht="15.75"/>
+    <row r="52" ht="15.75"/>
+    <row r="53" ht="15.75"/>
+    <row r="54" ht="15.75"/>
+    <row r="55" ht="15.75"/>
+    <row r="56" ht="15.75"/>
+    <row r="57" ht="15.75"/>
+    <row r="58" ht="15.75"/>
+    <row r="59" ht="15.75"/>
+    <row r="60" ht="15.75"/>
+    <row r="61" ht="15.75"/>
+    <row r="62" ht="15.75"/>
+    <row r="63" ht="15.75"/>
+    <row r="64" ht="15.75"/>
+    <row r="65" ht="15.75"/>
+    <row r="66" ht="15.75"/>
+    <row r="67" ht="15.75"/>
+    <row r="68" ht="15.75"/>
+    <row r="69" ht="15.75"/>
+    <row r="70" ht="15.75"/>
+    <row r="71" ht="15.75"/>
+    <row r="72" ht="15.75"/>
+    <row r="73" ht="15.75"/>
+    <row r="74" ht="15.75"/>
+    <row r="75" ht="15.75"/>
+    <row r="76" ht="15.75"/>
+    <row r="77" ht="15.75"/>
+    <row r="78" ht="15.75"/>
+    <row r="79" ht="15.75"/>
+    <row r="80" ht="15.75"/>
+    <row r="81" ht="15.75"/>
+    <row r="82" ht="15.75"/>
+    <row r="83" ht="15.75"/>
+    <row r="84" ht="15.75"/>
+    <row r="85" ht="15.75"/>
   </sheetData>
+  <conditionalFormatting sqref="C11:Z33">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B11,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:Z39">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(C$8&lt;&gt;"",IFERROR(INDEX(_ServerFieldMatrix,MATCH($B37,_ServerFieldLabels,0),MATCH(C$8,_ServerTypes,0)),"")="")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="G4:AE43 C4:F7 C9:F45 C48:F53 C67:F85 C56:F59 C62:F64" xr:uid="{AEB39A8F-9810-ED4E-9F27-465756D4623D}"/>
-    <dataValidation type="list" allowBlank="1" sqref="C8:F8" xr:uid="{DF709D8D-57D8-6842-9BBE-389F6303D2F1}">
-      <formula1>"api,athena,azure,bigquery,clickhouse,databricks,db2,denodo,dremio,duckdb,glue,cloudsql,informix,kafka,kinesis,mysql,local,oracle,postgresql,presto,pubsub,redshift,s3,sftp,snowflake,sqlserver,synapse,trino,vertica,custom"</formula1>
+    <dataValidation allowBlank="1" sqref="AA4:AE9" xr:uid="{AEB39A8F-9810-ED4E-9F27-465756D4623D}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:Z8" xr:uid="{E551C1DD-B145-4F53-AB5E-CC9BF68F020F}">
+      <formula1>_ServerTypes</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95CB51A-C5C4-224E-AA94-69EA1F503FF6}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="22" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="22" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="22"/>
+    <col min="1" max="1" width="26.140625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="22" customWidth="1"/>
+    <col min="3" max="16384" width="10.85546875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="24">
       <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A2" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="15.95"/>
+    <row r="4" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A4" s="7" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A5" s="7" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="15.95">
       <c r="A6" s="7" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="B6" s="5"/>
     </row>
@@ -2504,274 +4076,1361 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29635FC6-19E5-6E43-84D3-3161FAC792B3}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="90" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="3" width="28.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="57.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.5703125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="28.5703125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24">
       <c r="A1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="5" t="str">
+        <v>190</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="5" t="str">
         <f>IF(owner &lt;&gt; "", owner, "")</f>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:B61" xr:uid="{39D00745-E29F-BB4D-8EFF-9275524C1814}"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{E30C1BD1-16F4-4AA7-9E13-3DBE04CBD7DC}">
+      <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E1000" xr:uid="{B811DB7E-D176-4E46-A531-A1412060B856}">
+      <formula1>"Text,JSON"</formula1>
+    </dataValidation>
   </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F1501D-7108-45AA-A502-5C6A70801173}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{BA5D597E-E835-4437-8821-BCE2B6130694}">
+      <formula1>"Contract,Description,Server,Schema,Property,Quality,Support,Team,Team Member,Role,SLA,Relationship,Enum Value,Synonym,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D1000" xr:uid="{319D7A4C-096E-46E8-8009-AA150988F5BB}">
+      <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB36AF8D-77B7-4D59-850B-FF12E0D86C6F}">
+  <dimension ref="A1:AS24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:45">
+      <c r="A1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L1" t="s">
+        <v>206</v>
+      </c>
+      <c r="M1" t="s">
+        <v>207</v>
+      </c>
+      <c r="N1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O1" t="s">
+        <v>209</v>
+      </c>
+      <c r="P1" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>211</v>
+      </c>
+      <c r="R1" t="s">
+        <v>212</v>
+      </c>
+      <c r="S1" t="s">
+        <v>213</v>
+      </c>
+      <c r="T1" t="s">
+        <v>214</v>
+      </c>
+      <c r="U1" t="s">
+        <v>215</v>
+      </c>
+      <c r="V1" t="s">
+        <v>216</v>
+      </c>
+      <c r="W1" t="s">
+        <v>217</v>
+      </c>
+      <c r="X1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>224</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>235</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>236</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45">
+      <c r="A2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>241</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45">
+      <c r="A3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H3" t="s">
+        <v>240</v>
+      </c>
+      <c r="S3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>241</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45">
+      <c r="A4" t="s">
+        <v>162</v>
+      </c>
+      <c r="S4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="A5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" t="s">
+        <v>240</v>
+      </c>
+      <c r="I5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" t="s">
+        <v>240</v>
+      </c>
+      <c r="M5" t="s">
+        <v>240</v>
+      </c>
+      <c r="N5" t="s">
+        <v>240</v>
+      </c>
+      <c r="O5" t="s">
+        <v>241</v>
+      </c>
+      <c r="P5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>240</v>
+      </c>
+      <c r="R5" t="s">
+        <v>240</v>
+      </c>
+      <c r="T5" t="s">
+        <v>240</v>
+      </c>
+      <c r="U5" t="s">
+        <v>240</v>
+      </c>
+      <c r="V5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45">
+      <c r="A8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="N8" t="s">
+        <v>241</v>
+      </c>
+      <c r="W8" t="s">
+        <v>241</v>
+      </c>
+      <c r="X8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>240</v>
+      </c>
+      <c r="N10" t="s">
+        <v>241</v>
+      </c>
+      <c r="W10" t="s">
+        <v>241</v>
+      </c>
+      <c r="X10" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>241</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="A11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" t="s">
+        <v>240</v>
+      </c>
+      <c r="H11" t="s">
+        <v>241</v>
+      </c>
+      <c r="I11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J11" t="s">
+        <v>240</v>
+      </c>
+      <c r="L11" t="s">
+        <v>240</v>
+      </c>
+      <c r="M11" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" t="s">
+        <v>240</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>240</v>
+      </c>
+      <c r="R11" t="s">
+        <v>240</v>
+      </c>
+      <c r="T11" t="s">
+        <v>240</v>
+      </c>
+      <c r="U11" t="s">
+        <v>240</v>
+      </c>
+      <c r="V11" t="s">
+        <v>240</v>
+      </c>
+      <c r="W11" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>241</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>241</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="A12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>240</v>
+      </c>
+      <c r="N12" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45">
+      <c r="A13" t="s">
+        <v>170</v>
+      </c>
+      <c r="S13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45">
+      <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45">
+      <c r="A15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F15" t="s">
+        <v>241</v>
+      </c>
+      <c r="G15" t="s">
+        <v>240</v>
+      </c>
+      <c r="I15" t="s">
+        <v>240</v>
+      </c>
+      <c r="J15" t="s">
+        <v>240</v>
+      </c>
+      <c r="L15" t="s">
+        <v>241</v>
+      </c>
+      <c r="M15" t="s">
+        <v>241</v>
+      </c>
+      <c r="O15" t="s">
+        <v>241</v>
+      </c>
+      <c r="P15" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>240</v>
+      </c>
+      <c r="R15" t="s">
+        <v>241</v>
+      </c>
+      <c r="T15" t="s">
+        <v>241</v>
+      </c>
+      <c r="U15" t="s">
+        <v>241</v>
+      </c>
+      <c r="V15" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="X17" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45">
+      <c r="A18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>240</v>
+      </c>
+      <c r="H19" t="s">
+        <v>240</v>
+      </c>
+      <c r="J19" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" t="s">
+        <v>241</v>
+      </c>
+      <c r="L19" t="s">
+        <v>241</v>
+      </c>
+      <c r="O19" t="s">
+        <v>241</v>
+      </c>
+      <c r="P19" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45">
+      <c r="A20" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45">
+      <c r="A21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45">
+      <c r="A22" t="s">
+        <v>178</v>
+      </c>
+      <c r="X22" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45">
+      <c r="A23" t="s">
+        <v>179</v>
+      </c>
+      <c r="S23" t="s">
+        <v>241</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45">
+      <c r="A24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ABE851-FB8B-2145-B7F8-5CF6722D55A6}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="45" style="2" customWidth="1"/>
-    <col min="4" max="4" width="1.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="1.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="2" customWidth="1"/>
     <col min="7" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="23.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="2"/>
+    <col min="9" max="9" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="24">
       <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="35"/>
       <c r="C12" s="5"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="5"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="7" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="5"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B18" s="7"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="5"/>
+    </row>
+    <row r="25" spans="1:3" ht="15.75">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2794,369 +5453,297 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AR54"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.7109375" style="2" customWidth="1"/>
     <col min="7" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="28.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="19" style="2" customWidth="1"/>
-    <col min="21" max="21" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="37" width="15.5" style="2" customWidth="1"/>
-    <col min="38" max="38" width="26.1640625" style="2" customWidth="1"/>
-    <col min="39" max="16384" width="8.83203125" style="2"/>
+    <col min="9" max="9" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="21" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="28.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.7109375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="19" style="2" customWidth="1"/>
+    <col min="23" max="23" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="39" width="15.42578125" style="2" customWidth="1"/>
+    <col min="40" max="40" width="21" style="2" customWidth="1"/>
+    <col min="41" max="41" width="28.5703125" style="2" customWidth="1"/>
+    <col min="42" max="44" width="26.7109375" style="2" customWidth="1"/>
+    <col min="45" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="24">
       <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44">
       <c r="A2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44">
       <c r="A3" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
       <c r="E5" s="36"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44">
       <c r="A6" s="7" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44">
       <c r="A7" s="7" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B7" s="36"/>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44">
       <c r="A8" s="7" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B8" s="37"/>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44">
       <c r="A9" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="37"/>
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
       <c r="E9" s="39"/>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44">
       <c r="A10" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="37"/>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
       <c r="E10" s="39"/>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44">
       <c r="A11" s="7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="W12" s="19" t="s">
+    <row r="12" spans="1:44">
+      <c r="A12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45"/>
+    </row>
+    <row r="13" spans="1:44">
+      <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
+    </row>
+    <row r="14" spans="1:44">
+      <c r="A14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="45"/>
+    </row>
+    <row r="15" spans="1:44">
+      <c r="Y15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="20"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="20"/>
+      <c r="AM15" s="21"/>
+      <c r="AN15" s="40"/>
+      <c r="AP15" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ15" s="42"/>
+      <c r="AR15" s="42"/>
+    </row>
+    <row r="16" spans="1:44">
+      <c r="A16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="P16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="V16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="X16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z16" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB16" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
-      <c r="AE12" s="20"/>
-      <c r="AF12" s="20"/>
-      <c r="AG12" s="20"/>
-      <c r="AH12" s="20"/>
-      <c r="AI12" s="20"/>
-      <c r="AJ12" s="20"/>
-      <c r="AK12" s="21"/>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="T13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="U13" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="V13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="W13" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="X13" s="10" t="s">
+      <c r="AC16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="Y13" s="10" t="s">
+      <c r="AD16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="Z13" s="10" t="s">
+      <c r="AE16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AA13" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB13" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC13" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD13" s="10" t="s">
+      <c r="AF16" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH16" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AE13" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG13" s="10" t="s">
+      <c r="AI16" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AH13" s="10" t="s">
+      <c r="AJ16" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK16" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="AI13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ13" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK13" s="10" t="s">
+      <c r="AL16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AL13" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="15"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="15"/>
-      <c r="AF14" s="15"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="15"/>
-      <c r="AI14" s="15"/>
-      <c r="AJ14" s="15"/>
-      <c r="AK14" s="15"/>
-      <c r="AL14" s="28"/>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="15"/>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="15"/>
-      <c r="AG15" s="15"/>
-      <c r="AH15" s="15"/>
-      <c r="AI15" s="15"/>
-      <c r="AJ15" s="15"/>
-      <c r="AK15" s="15"/>
-      <c r="AL15" s="28"/>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A16" s="17"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="15"/>
-      <c r="AK16" s="15"/>
-      <c r="AL16" s="28"/>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP16" s="9"/>
+      <c r="AQ16" s="9"/>
+      <c r="AR16" s="9"/>
+    </row>
+    <row r="17" spans="1:44">
       <c r="A17" s="17"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -3194,9 +5781,15 @@
       <c r="AI17" s="15"/>
       <c r="AJ17" s="15"/>
       <c r="AK17" s="15"/>
-      <c r="AL17" s="28"/>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="15"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44">
       <c r="A18" s="17"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -3234,9 +5827,15 @@
       <c r="AI18" s="15"/>
       <c r="AJ18" s="15"/>
       <c r="AK18" s="15"/>
-      <c r="AL18" s="28"/>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL18" s="15"/>
+      <c r="AM18" s="15"/>
+      <c r="AN18" s="15"/>
+      <c r="AO18" s="15"/>
+      <c r="AP18" s="15"/>
+      <c r="AQ18" s="15"/>
+      <c r="AR18" s="15"/>
+    </row>
+    <row r="19" spans="1:44">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -3274,9 +5873,15 @@
       <c r="AI19" s="15"/>
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
-      <c r="AL19" s="28"/>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL19" s="15"/>
+      <c r="AM19" s="15"/>
+      <c r="AN19" s="15"/>
+      <c r="AO19" s="15"/>
+      <c r="AP19" s="15"/>
+      <c r="AQ19" s="15"/>
+      <c r="AR19" s="15"/>
+    </row>
+    <row r="20" spans="1:44">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -3314,10 +5919,16 @@
       <c r="AI20" s="15"/>
       <c r="AJ20" s="15"/>
       <c r="AK20" s="15"/>
-      <c r="AL20" s="28"/>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
+      <c r="AL20" s="15"/>
+      <c r="AM20" s="15"/>
+      <c r="AN20" s="15"/>
+      <c r="AO20" s="15"/>
+      <c r="AP20" s="15"/>
+      <c r="AQ20" s="15"/>
+      <c r="AR20" s="15"/>
+    </row>
+    <row r="21" spans="1:44">
+      <c r="A21" s="17"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -3354,10 +5965,16 @@
       <c r="AI21" s="15"/>
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
-      <c r="AL21" s="28"/>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
+      <c r="AL21" s="15"/>
+      <c r="AM21" s="15"/>
+      <c r="AN21" s="15"/>
+      <c r="AO21" s="15"/>
+      <c r="AP21" s="15"/>
+      <c r="AQ21" s="15"/>
+      <c r="AR21" s="15"/>
+    </row>
+    <row r="22" spans="1:44">
+      <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -3394,10 +6011,16 @@
       <c r="AI22" s="15"/>
       <c r="AJ22" s="15"/>
       <c r="AK22" s="15"/>
-      <c r="AL22" s="28"/>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
+      <c r="AL22" s="15"/>
+      <c r="AM22" s="15"/>
+      <c r="AN22" s="15"/>
+      <c r="AO22" s="15"/>
+      <c r="AP22" s="15"/>
+      <c r="AQ22" s="15"/>
+      <c r="AR22" s="15"/>
+    </row>
+    <row r="23" spans="1:44">
+      <c r="A23" s="17"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -3434,10 +6057,16 @@
       <c r="AI23" s="15"/>
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
-      <c r="AL23" s="28"/>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
+      <c r="AL23" s="15"/>
+      <c r="AM23" s="15"/>
+      <c r="AN23" s="15"/>
+      <c r="AO23" s="15"/>
+      <c r="AP23" s="15"/>
+      <c r="AQ23" s="15"/>
+      <c r="AR23" s="15"/>
+    </row>
+    <row r="24" spans="1:44">
+      <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -3474,10 +6103,16 @@
       <c r="AI24" s="15"/>
       <c r="AJ24" s="15"/>
       <c r="AK24" s="15"/>
-      <c r="AL24" s="28"/>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="15"/>
+      <c r="AN24" s="15"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44">
+      <c r="A25" s="18"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -3514,10 +6149,16 @@
       <c r="AI25" s="15"/>
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
-      <c r="AL25" s="28"/>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
+      <c r="AL25" s="15"/>
+      <c r="AM25" s="15"/>
+      <c r="AN25" s="15"/>
+      <c r="AO25" s="15"/>
+      <c r="AP25" s="15"/>
+      <c r="AQ25" s="15"/>
+      <c r="AR25" s="15"/>
+    </row>
+    <row r="26" spans="1:44">
+      <c r="A26" s="18"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -3554,9 +6195,15 @@
       <c r="AI26" s="15"/>
       <c r="AJ26" s="15"/>
       <c r="AK26" s="15"/>
-      <c r="AL26" s="28"/>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL26" s="15"/>
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+      <c r="AO26" s="15"/>
+      <c r="AP26" s="15"/>
+      <c r="AQ26" s="15"/>
+      <c r="AR26" s="15"/>
+    </row>
+    <row r="27" spans="1:44">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -3594,9 +6241,15 @@
       <c r="AI27" s="15"/>
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
-      <c r="AL27" s="28"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
+    <row r="28" spans="1:44">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -3634,9 +6287,15 @@
       <c r="AI28" s="15"/>
       <c r="AJ28" s="15"/>
       <c r="AK28" s="15"/>
-      <c r="AL28" s="28"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL28" s="15"/>
+      <c r="AM28" s="15"/>
+      <c r="AN28" s="15"/>
+      <c r="AO28" s="15"/>
+      <c r="AP28" s="15"/>
+      <c r="AQ28" s="15"/>
+      <c r="AR28" s="15"/>
+    </row>
+    <row r="29" spans="1:44">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -3674,9 +6333,15 @@
       <c r="AI29" s="15"/>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
-      <c r="AL29" s="28"/>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL29" s="15"/>
+      <c r="AM29" s="15"/>
+      <c r="AN29" s="15"/>
+      <c r="AO29" s="15"/>
+      <c r="AP29" s="15"/>
+      <c r="AQ29" s="15"/>
+      <c r="AR29" s="15"/>
+    </row>
+    <row r="30" spans="1:44">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -3714,9 +6379,15 @@
       <c r="AI30" s="15"/>
       <c r="AJ30" s="15"/>
       <c r="AK30" s="15"/>
-      <c r="AL30" s="28"/>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL30" s="15"/>
+      <c r="AM30" s="15"/>
+      <c r="AN30" s="15"/>
+      <c r="AO30" s="15"/>
+      <c r="AP30" s="15"/>
+      <c r="AQ30" s="15"/>
+      <c r="AR30" s="15"/>
+    </row>
+    <row r="31" spans="1:44">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -3754,9 +6425,15 @@
       <c r="AI31" s="15"/>
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
-      <c r="AL31" s="28"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL31" s="15"/>
+      <c r="AM31" s="15"/>
+      <c r="AN31" s="15"/>
+      <c r="AO31" s="15"/>
+      <c r="AP31" s="15"/>
+      <c r="AQ31" s="15"/>
+      <c r="AR31" s="15"/>
+    </row>
+    <row r="32" spans="1:44">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -3794,9 +6471,15 @@
       <c r="AI32" s="15"/>
       <c r="AJ32" s="15"/>
       <c r="AK32" s="15"/>
-      <c r="AL32" s="28"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL32" s="15"/>
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+      <c r="AO32" s="15"/>
+      <c r="AP32" s="15"/>
+      <c r="AQ32" s="15"/>
+      <c r="AR32" s="15"/>
+    </row>
+    <row r="33" spans="1:44">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -3834,9 +6517,15 @@
       <c r="AI33" s="15"/>
       <c r="AJ33" s="15"/>
       <c r="AK33" s="15"/>
-      <c r="AL33" s="28"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+      <c r="AO33" s="15"/>
+      <c r="AP33" s="15"/>
+      <c r="AQ33" s="15"/>
+      <c r="AR33" s="15"/>
+    </row>
+    <row r="34" spans="1:44">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -3874,9 +6563,15 @@
       <c r="AI34" s="15"/>
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
-      <c r="AL34" s="28"/>
-    </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL34" s="15"/>
+      <c r="AM34" s="15"/>
+      <c r="AN34" s="15"/>
+      <c r="AO34" s="15"/>
+      <c r="AP34" s="15"/>
+      <c r="AQ34" s="15"/>
+      <c r="AR34" s="15"/>
+    </row>
+    <row r="35" spans="1:44">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -3914,9 +6609,15 @@
       <c r="AI35" s="15"/>
       <c r="AJ35" s="15"/>
       <c r="AK35" s="15"/>
-      <c r="AL35" s="28"/>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL35" s="15"/>
+      <c r="AM35" s="15"/>
+      <c r="AN35" s="15"/>
+      <c r="AO35" s="15"/>
+      <c r="AP35" s="15"/>
+      <c r="AQ35" s="15"/>
+      <c r="AR35" s="15"/>
+    </row>
+    <row r="36" spans="1:44">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -3954,9 +6655,15 @@
       <c r="AI36" s="15"/>
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
-      <c r="AL36" s="28"/>
-    </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL36" s="15"/>
+      <c r="AM36" s="15"/>
+      <c r="AN36" s="15"/>
+      <c r="AO36" s="15"/>
+      <c r="AP36" s="15"/>
+      <c r="AQ36" s="15"/>
+      <c r="AR36" s="15"/>
+    </row>
+    <row r="37" spans="1:44">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -3994,9 +6701,15 @@
       <c r="AI37" s="15"/>
       <c r="AJ37" s="15"/>
       <c r="AK37" s="15"/>
-      <c r="AL37" s="28"/>
-    </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL37" s="15"/>
+      <c r="AM37" s="15"/>
+      <c r="AN37" s="15"/>
+      <c r="AO37" s="15"/>
+      <c r="AP37" s="15"/>
+      <c r="AQ37" s="15"/>
+      <c r="AR37" s="15"/>
+    </row>
+    <row r="38" spans="1:44">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -4034,9 +6747,15 @@
       <c r="AI38" s="15"/>
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
-      <c r="AL38" s="28"/>
-    </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL38" s="15"/>
+      <c r="AM38" s="15"/>
+      <c r="AN38" s="15"/>
+      <c r="AO38" s="15"/>
+      <c r="AP38" s="15"/>
+      <c r="AQ38" s="15"/>
+      <c r="AR38" s="15"/>
+    </row>
+    <row r="39" spans="1:44">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -4074,9 +6793,15 @@
       <c r="AI39" s="15"/>
       <c r="AJ39" s="15"/>
       <c r="AK39" s="15"/>
-      <c r="AL39" s="28"/>
-    </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL39" s="15"/>
+      <c r="AM39" s="15"/>
+      <c r="AN39" s="15"/>
+      <c r="AO39" s="15"/>
+      <c r="AP39" s="15"/>
+      <c r="AQ39" s="15"/>
+      <c r="AR39" s="15"/>
+    </row>
+    <row r="40" spans="1:44">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -4114,9 +6839,15 @@
       <c r="AI40" s="15"/>
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
-      <c r="AL40" s="28"/>
-    </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL40" s="15"/>
+      <c r="AM40" s="15"/>
+      <c r="AN40" s="15"/>
+      <c r="AO40" s="15"/>
+      <c r="AP40" s="15"/>
+      <c r="AQ40" s="15"/>
+      <c r="AR40" s="15"/>
+    </row>
+    <row r="41" spans="1:44">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -4154,9 +6885,15 @@
       <c r="AI41" s="15"/>
       <c r="AJ41" s="15"/>
       <c r="AK41" s="15"/>
-      <c r="AL41" s="28"/>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL41" s="15"/>
+      <c r="AM41" s="15"/>
+      <c r="AN41" s="15"/>
+      <c r="AO41" s="15"/>
+      <c r="AP41" s="15"/>
+      <c r="AQ41" s="15"/>
+      <c r="AR41" s="15"/>
+    </row>
+    <row r="42" spans="1:44">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -4194,9 +6931,15 @@
       <c r="AI42" s="15"/>
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
-      <c r="AL42" s="28"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL42" s="15"/>
+      <c r="AM42" s="15"/>
+      <c r="AN42" s="15"/>
+      <c r="AO42" s="15"/>
+      <c r="AP42" s="15"/>
+      <c r="AQ42" s="15"/>
+      <c r="AR42" s="15"/>
+    </row>
+    <row r="43" spans="1:44">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4234,9 +6977,15 @@
       <c r="AI43" s="15"/>
       <c r="AJ43" s="15"/>
       <c r="AK43" s="15"/>
-      <c r="AL43" s="28"/>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL43" s="15"/>
+      <c r="AM43" s="15"/>
+      <c r="AN43" s="15"/>
+      <c r="AO43" s="15"/>
+      <c r="AP43" s="15"/>
+      <c r="AQ43" s="15"/>
+      <c r="AR43" s="15"/>
+    </row>
+    <row r="44" spans="1:44">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4274,9 +7023,15 @@
       <c r="AI44" s="15"/>
       <c r="AJ44" s="15"/>
       <c r="AK44" s="15"/>
-      <c r="AL44" s="28"/>
-    </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL44" s="15"/>
+      <c r="AM44" s="15"/>
+      <c r="AN44" s="15"/>
+      <c r="AO44" s="15"/>
+      <c r="AP44" s="15"/>
+      <c r="AQ44" s="15"/>
+      <c r="AR44" s="15"/>
+    </row>
+    <row r="45" spans="1:44">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4314,9 +7069,15 @@
       <c r="AI45" s="15"/>
       <c r="AJ45" s="15"/>
       <c r="AK45" s="15"/>
-      <c r="AL45" s="28"/>
-    </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL45" s="15"/>
+      <c r="AM45" s="15"/>
+      <c r="AN45" s="15"/>
+      <c r="AO45" s="15"/>
+      <c r="AP45" s="15"/>
+      <c r="AQ45" s="15"/>
+      <c r="AR45" s="15"/>
+    </row>
+    <row r="46" spans="1:44">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4354,9 +7115,15 @@
       <c r="AI46" s="15"/>
       <c r="AJ46" s="15"/>
       <c r="AK46" s="15"/>
-      <c r="AL46" s="28"/>
-    </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL46" s="15"/>
+      <c r="AM46" s="15"/>
+      <c r="AN46" s="15"/>
+      <c r="AO46" s="15"/>
+      <c r="AP46" s="15"/>
+      <c r="AQ46" s="15"/>
+      <c r="AR46" s="15"/>
+    </row>
+    <row r="47" spans="1:44">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4394,9 +7161,15 @@
       <c r="AI47" s="15"/>
       <c r="AJ47" s="15"/>
       <c r="AK47" s="15"/>
-      <c r="AL47" s="28"/>
-    </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL47" s="15"/>
+      <c r="AM47" s="15"/>
+      <c r="AN47" s="15"/>
+      <c r="AO47" s="15"/>
+      <c r="AP47" s="15"/>
+      <c r="AQ47" s="15"/>
+      <c r="AR47" s="15"/>
+    </row>
+    <row r="48" spans="1:44">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4434,9 +7207,15 @@
       <c r="AI48" s="15"/>
       <c r="AJ48" s="15"/>
       <c r="AK48" s="15"/>
-      <c r="AL48" s="28"/>
-    </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AL48" s="15"/>
+      <c r="AM48" s="15"/>
+      <c r="AN48" s="15"/>
+      <c r="AO48" s="15"/>
+      <c r="AP48" s="15"/>
+      <c r="AQ48" s="15"/>
+      <c r="AR48" s="15"/>
+    </row>
+    <row r="49" spans="1:44">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4474,10 +7253,160 @@
       <c r="AI49" s="15"/>
       <c r="AJ49" s="15"/>
       <c r="AK49" s="15"/>
-      <c r="AL49" s="28"/>
-    </row>
+      <c r="AL49" s="15"/>
+      <c r="AM49" s="15"/>
+      <c r="AN49" s="15"/>
+      <c r="AO49" s="15"/>
+      <c r="AP49" s="15"/>
+      <c r="AQ49" s="15"/>
+      <c r="AR49" s="15"/>
+    </row>
+    <row r="50" spans="1:44">
+      <c r="A50" s="17"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15"/>
+      <c r="R50" s="15"/>
+      <c r="S50" s="15"/>
+      <c r="T50" s="15"/>
+      <c r="U50" s="15"/>
+      <c r="V50" s="15"/>
+      <c r="W50" s="15"/>
+      <c r="X50" s="15"/>
+      <c r="Y50" s="15"/>
+      <c r="Z50" s="15"/>
+      <c r="AA50" s="15"/>
+      <c r="AB50" s="15"/>
+      <c r="AC50" s="15"/>
+      <c r="AD50" s="15"/>
+      <c r="AE50" s="15"/>
+      <c r="AF50" s="15"/>
+      <c r="AG50" s="15"/>
+      <c r="AH50" s="15"/>
+      <c r="AI50" s="15"/>
+      <c r="AJ50" s="15"/>
+      <c r="AK50" s="15"/>
+      <c r="AL50" s="15"/>
+      <c r="AM50" s="15"/>
+      <c r="AN50" s="15"/>
+      <c r="AO50" s="15"/>
+      <c r="AP50" s="15"/>
+      <c r="AQ50" s="15"/>
+      <c r="AR50" s="15"/>
+    </row>
+    <row r="51" spans="1:44">
+      <c r="A51" s="17"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="15"/>
+      <c r="S51" s="15"/>
+      <c r="T51" s="15"/>
+      <c r="U51" s="15"/>
+      <c r="V51" s="15"/>
+      <c r="W51" s="15"/>
+      <c r="X51" s="15"/>
+      <c r="Y51" s="15"/>
+      <c r="Z51" s="15"/>
+      <c r="AA51" s="15"/>
+      <c r="AB51" s="15"/>
+      <c r="AC51" s="15"/>
+      <c r="AD51" s="15"/>
+      <c r="AE51" s="15"/>
+      <c r="AF51" s="15"/>
+      <c r="AG51" s="15"/>
+      <c r="AH51" s="15"/>
+      <c r="AI51" s="15"/>
+      <c r="AJ51" s="15"/>
+      <c r="AK51" s="15"/>
+      <c r="AL51" s="15"/>
+      <c r="AM51" s="15"/>
+      <c r="AN51" s="15"/>
+      <c r="AO51" s="15"/>
+      <c r="AP51" s="15"/>
+      <c r="AQ51" s="15"/>
+      <c r="AR51" s="15"/>
+    </row>
+    <row r="52" spans="1:44">
+      <c r="A52" s="17"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="15"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="15"/>
+      <c r="T52" s="15"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="15"/>
+      <c r="W52" s="15"/>
+      <c r="X52" s="15"/>
+      <c r="Y52" s="15"/>
+      <c r="Z52" s="15"/>
+      <c r="AA52" s="15"/>
+      <c r="AB52" s="15"/>
+      <c r="AC52" s="15"/>
+      <c r="AD52" s="15"/>
+      <c r="AE52" s="15"/>
+      <c r="AF52" s="15"/>
+      <c r="AG52" s="15"/>
+      <c r="AH52" s="15"/>
+      <c r="AI52" s="15"/>
+      <c r="AJ52" s="15"/>
+      <c r="AK52" s="15"/>
+      <c r="AL52" s="15"/>
+      <c r="AM52" s="15"/>
+      <c r="AN52" s="15"/>
+      <c r="AO52" s="15"/>
+      <c r="AP52" s="15"/>
+      <c r="AQ52" s="15"/>
+      <c r="AR52" s="15"/>
+    </row>
+    <row r="53" spans="1:44"/>
+    <row r="54" spans="1:44"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
@@ -4486,30 +7415,35 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H14:H49" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H17:H52" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C49" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
-      <formula1>"string,number,integer,boolean,array,object,timestamp,date,time"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" sqref="B14:B49 J14:J49 M14:U49 W14:AL49" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G14:G49" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
+    <dataValidation allowBlank="1" sqref="B17:B52 L17:L52 O17:W52 Y17:AN52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Schema Name" prompt="The name of the schema (e.g., table) must match the Sheet name &quot;Schema &lt;schema_name&gt;&quot;" sqref="B5:E5" xr:uid="{8B3F718D-6361-B845-86DC-2F310C7348A9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A13" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="L14:L49" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A16" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="N17:N52" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
       <formula1>"businessDefinition,transformationImplementation,videoTutorial,tutorial,implementation"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I14:I49" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I52" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
       <formula1>"confidential,restricted,public"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="K14:K49" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
-    <dataValidation type="list" allowBlank="1" sqref="V14:V49" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="M17:M52" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
+    <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AL13" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 J17:J52" xr:uid="{5951D012-9713-4BF9-B49A-36D7824469E7}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K17:K52" xr:uid="{5C060A55-B19E-4700-8202-4FE63BD6E0A6}">
+      <formula1>"column,measure,dimension"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{BD7CBF6C-981D-40E3-9447-A74CA1C2780C}">
+      <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4517,177 +7451,235 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0C8C2B4-64D3-DB4C-BBDA-0F192B30B9A9}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="13" style="30" customWidth="1"/>
-    <col min="3" max="3" width="48.5" style="30" customWidth="1"/>
-    <col min="4" max="4" width="42.83203125" style="30" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" style="30" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="30"/>
+    <col min="1" max="1" width="8.28515625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="13" style="29" customWidth="1"/>
+    <col min="3" max="3" width="48.42578125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="42.85546875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="29" customWidth="1"/>
+    <col min="6" max="8" width="26.7109375" style="29" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" s="31"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="31"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="24">
+      <c r="A1" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75">
+      <c r="A2" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="30"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="F3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>C5="sql"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
   <dataValidations count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="A human-readable description of the relationship. Explain the business context or purpose of how the source and target are related." sqref="E4" xr:uid="{EE4A1054-F15A-664C-B875-762503081248}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Type" prompt="Type of the relationship column(s)." sqref="B4" xr:uid="{41A27CD9-820D-2E48-B8C9-300C785AF670}"/>
@@ -4708,84 +7700,1131 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0086E894-DDEF-454E-BBEC-466C190BF33C}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22" style="30" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="30" customWidth="1"/>
-    <col min="7" max="7" width="19" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" style="30" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="30"/>
+    <col min="1" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" customWidth="1"/>
+    <col min="6" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="10" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="29"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="31"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75">
+      <c r="H3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC387154-8B4D-4EA8-8294-5AF954FB5535}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" customWidth="1"/>
+    <col min="5" max="8" width="28.5703125" customWidth="1"/>
+    <col min="9" max="11" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75">
+      <c r="I3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+    </row>
+    <row r="15" spans="1:11" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE481688-B3AC-4CED-871E-24F494244609}">
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="4" width="57.140625" customWidth="1"/>
+    <col min="5" max="6" width="28.5703125" customWidth="1"/>
+    <col min="7" max="9" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75">
+      <c r="G3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{410BAB73-2EB0-4EA5-B7D4-D0794210AFC3}">
+      <formula1>"Contract,Schema"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FA52E6-D20E-4DFD-9B9D-0129E3657275}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="66.7109375" customWidth="1"/>
+    <col min="4" max="5" width="28.5703125" customWidth="1"/>
+    <col min="6" max="8" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="F3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A1000" xr:uid="{6C62E592-567C-4D75-BC42-BA79D40F91CF}">
+      <formula1>"Contract,Schema"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="22" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="29" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="19" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="29" customWidth="1"/>
+    <col min="14" max="14" width="28.5703125" style="29" customWidth="1"/>
+    <col min="15" max="17" width="26.7109375" style="29" customWidth="1"/>
+    <col min="18" max="16384" width="8.85546875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="24">
+      <c r="A1" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75">
+      <c r="A2" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="30"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="O3" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.75">
+      <c r="A4" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="15"/>
@@ -4799,8 +8838,12 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="15"/>
@@ -4814,8 +8857,12 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="15"/>
@@ -4829,8 +8876,12 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="15"/>
@@ -4844,8 +8895,12 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
       <c r="C9" s="15"/>
@@ -4859,8 +8914,12 @@
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="15"/>
@@ -4874,8 +8933,12 @@
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
       <c r="C11" s="15"/>
@@ -4889,8 +8952,12 @@
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
       <c r="C12" s="15"/>
@@ -4904,8 +8971,12 @@
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="15"/>
@@ -4919,8 +8990,12 @@
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="15"/>
@@ -4934,8 +9009,12 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
       <c r="C15" s="15"/>
@@ -4949,8 +9028,12 @@
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="15"/>
@@ -4964,8 +9047,12 @@
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="15"/>
@@ -4979,8 +9066,12 @@
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="15"/>
@@ -4994,8 +9085,12 @@
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
       <c r="C19" s="15"/>
@@ -5009,8 +9104,12 @@
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="15"/>
@@ -5024,8 +9123,12 @@
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="15"/>
@@ -5039,15 +9142,22 @@
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="O3:Q3"/>
+  </mergeCells>
   <conditionalFormatting sqref="E5:E21">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>C5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F21">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>C5="library"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5077,758 +9187,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FB3633-F435-1B44-A99B-F400ACF77C57}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="6" width="23.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:F61" xr:uid="{19A11CF7-5A67-E844-8CDE-E9312B26965E}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="7" width="23.6640625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:G61" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:E61" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C18618-CA09-244F-9E12-D5D128AED5CE}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="32.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="26"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="B7:F63" xr:uid="{7F4EE529-7BE7-6547-817C-8DBC88D35FEC}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B4" xr:uid="{8220F424-DC29-F648-BD41-E75C77AE8B05}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>